--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -2,8 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Users Module Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13,90 +23,41 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color theme="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1C4587"/>
-        <bgColor rgb="FF1C4587"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
-    <border/>
+  <borders count="2">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -108,31 +69,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -205,20 +154,20 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -242,19 +191,77 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -266,158 +273,190 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16.29" customWidth="1" style="6" min="1" max="1"/>
-    <col width="15.57" customWidth="1" style="6" min="2" max="2"/>
-    <col width="22" customWidth="1" style="6" min="3" max="4"/>
-    <col width="28" customWidth="1" style="6" min="5" max="5"/>
-    <col width="32" customWidth="1" style="6" min="6" max="6"/>
-    <col width="38" customWidth="1" style="6" min="7" max="7"/>
-    <col width="18" customWidth="1" style="6" min="8" max="8"/>
-    <col width="8.710000000000001" customWidth="1" style="6" min="9" max="26"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="6">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
@@ -459,7 +498,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="62.25" customHeight="1" s="6">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_001</t>
@@ -503,15 +542,15 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="61.5" customHeight="1" s="6">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_002</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify alphabetical grouping of users</t>
@@ -535,15 +574,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="46.5" customHeight="1" s="6">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_003</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify user profile picture display</t>
@@ -566,15 +605,15 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="35.25" customHeight="1" s="6">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>USERS_004</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify user name display format</t>
@@ -597,7 +636,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="46.5" customHeight="1" s="6">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>USERS_005</t>
@@ -640,7 +679,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="49.5" customHeight="1" s="6">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>USERS_006</t>
@@ -684,7 +723,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="60.75" customHeight="1" s="6">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>USERS_007</t>
@@ -728,15 +767,15 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" s="6">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>USERS_008</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify selected user visual feedback</t>
@@ -760,7 +799,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1" s="6">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>USERS_009</t>
@@ -803,15 +842,15 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65.25" customHeight="1" s="6">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>USERS_010</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify search by full name</t>
@@ -836,15 +875,15 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="53.25" customHeight="1" s="6">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>USERS_011</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify search by partial first name</t>
@@ -868,15 +907,15 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="55.5" customHeight="1" s="6">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>USERS_012</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verify search by partial last name</t>
@@ -900,15 +939,15 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="46.5" customHeight="1" s="6">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>USERS_013</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
@@ -932,7 +971,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="6">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>USERS_014</t>
@@ -976,15 +1015,15 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="15.75" customHeight="1" s="6">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>USERS_015</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
@@ -1008,15 +1047,15 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="6">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>USERS_016</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify search with only spaces</t>
@@ -1040,7 +1079,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="15.75" customHeight="1" s="6">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>USERS_017</t>
@@ -1085,15 +1124,15 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="6">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>USERS_018</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
@@ -1117,15 +1156,15 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="6">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>USERS_019</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify search with minimum characters</t>
@@ -1149,7 +1188,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="6">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>USERS_020</t>
@@ -1193,15 +1232,15 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1" s="6">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>USERS_021</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify Users module on mobile device</t>
@@ -1225,7 +1264,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="6">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>USERS_022</t>
@@ -1268,15 +1307,15 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="6">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>USERS_023</t>
         </is>
       </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
@@ -1300,7 +1339,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="6">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>USERS_024</t>
@@ -1344,14 +1383,14 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="6">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>USERS_025</t>
         </is>
       </c>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
@@ -1380,1670 +1419,1099 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1" s="6">
-      <c r="A27" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_026</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: User Module with Chat</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify clicking user opens one-on-one chat</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Click on a user in the list.</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>One-on-one chat should open with that user. Message history should load.</t>
         </is>
       </c>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1" s="6">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_027</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr"/>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Integration: User Module with Conversation List</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify starting chat from users list creates conversation</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Click on a user with no prior conversation.
 2. Send a message.</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>New conversation should appear in conversation list after sending first message.</t>
         </is>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="6">
-      <c r="A29" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_028</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: User Module</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify user list updates when new user registers</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. A new user registers on the platform.
 2. Refresh user list.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>New user should appear in the user list.</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1" s="6">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_029</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr"/>
-      <c r="C30" s="9" t="inlineStr"/>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify user list after blocking a user</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Blocked user should be handled per policy (hidden, marked, or unchanged in list).</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1" s="6">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_030</t>
         </is>
       </c>
-      <c r="B31" s="9" t="inlineStr"/>
-      <c r="C31" s="9" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify user list after unblocking a user</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Unblock a previously blocked user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>User should be accessible again in the list.</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="6">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>USERS_031</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr"/>
-      <c r="C32" s="9" t="inlineStr"/>
-      <c r="D32" s="9" t="inlineStr"/>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify user online status updates in real-time</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Observe a user in the list.
 2. That user goes online/offline.</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Online status indicator should update in real-time.</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15.75" customHeight="1" s="6">
-      <c r="A33" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_032</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: User Module</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is not logged in</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify user list not accessible without authentication</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Try to access user list without logging in.</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should redirect to login. No user data exposed.</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15.75" customHeight="1" s="6">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_033</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr"/>
-      <c r="C34" s="9" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify user list does not expose sensitive user data</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe user list entries.</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Only public info (name, avatar, status) should display. No email, phone, or private data.</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1" s="6">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_034</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr"/>
-      <c r="C35" s="9" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify XSS prevention in user search</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Type '&lt;script&gt;alert(1)&lt;/script&gt;' in user search.</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Input should be sanitized. No script execution.</t>
         </is>
       </c>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="6">
-      <c r="A36" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_035</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: User Module</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify user list with 10000+ users</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open users tab on a platform with 10000+ users.</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Users should load with pagination/infinite scroll. Alphabetical grouping should work.</t>
         </is>
       </c>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15.75" customHeight="1" s="6">
-      <c r="A37" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_036</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr"/>
-      <c r="C37" s="9" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify user with very long name</t>
         </is>
       </c>
-      <c r="F37" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe a user with a 100+ character name in the list.</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Name should truncate with ellipsis. No layout breaking.</t>
         </is>
       </c>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15.75" customHeight="1" s="6">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_037</t>
         </is>
       </c>
-      <c r="B38" s="9" t="inlineStr"/>
-      <c r="C38" s="9" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr"/>
-      <c r="E38" s="9" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify user with special characters in name</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Observe a user with emojis, unicode, or special chars in name.</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Name should display correctly.</t>
         </is>
       </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="6">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>USERS_038</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr"/>
-      <c r="C39" s="9" t="inlineStr"/>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify user search with partial name</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Search for first 2 characters of a user's name.</t>
         </is>
       </c>
-      <c r="G39" s="9" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>All users matching the partial name should appear.</t>
         </is>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="15.75" customHeight="1" s="6">
-      <c r="A40" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>USERS_039</t>
         </is>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr"/>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="9" t="inlineStr">
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify user list when server returns error</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Simulate server error.
 2. Open users tab.</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Error message should display with retry option. No crash.</t>
         </is>
       </c>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="6">
-      <c r="A41" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_040</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: User Module</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify user list with exactly 0 users (only self)</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Login on a platform with no other users.</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Empty state should display or only self should appear.</t>
         </is>
       </c>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="15.75" customHeight="1" s="6">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_041</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr"/>
-      <c r="C42" s="9" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify user list with exactly 1 other user</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Login on a platform with 1 other user.</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Single user should display correctly with all elements.</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15.75" customHeight="1" s="6">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_042</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr"/>
-      <c r="C43" s="9" t="inlineStr"/>
-      <c r="D43" s="9" t="inlineStr"/>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search with exactly 1 character</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Type a single character in user search.</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should filter users or show minimum character requirement.</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15.75" customHeight="1" s="6">
-      <c r="A44" s="9" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>USERS_043</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: User Status</t>
         </is>
       </c>
-      <c r="D44" s="9" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E44" s="9" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify online user display</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Observe an online user in the list.</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should show green online indicator and be at top of list (if sorted by status).</t>
         </is>
       </c>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="6">
-      <c r="A45" s="9" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>USERS_044</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr"/>
-      <c r="C45" s="9" t="inlineStr"/>
-      <c r="D45" s="9" t="inlineStr"/>
-      <c r="E45" s="9" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify offline user display</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Observe an offline user in the list.</t>
         </is>
       </c>
-      <c r="G45" s="9" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should show grey/no indicator. Last seen time may display.</t>
         </is>
       </c>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="6">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>USERS_045</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr"/>
-      <c r="C46" s="9" t="inlineStr"/>
-      <c r="D46" s="9" t="inlineStr"/>
-      <c r="E46" s="9" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify away/busy user display (if supported)</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Observe a user with away/busy status.</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Should show appropriate status indicator (yellow/red dot).</t>
         </is>
       </c>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="6"/>
-    <row r="48" ht="15.75" customHeight="1" s="6"/>
-    <row r="49" ht="15.75" customHeight="1" s="6"/>
-    <row r="50" ht="15.75" customHeight="1" s="6"/>
-    <row r="51" ht="15.75" customHeight="1" s="6"/>
-    <row r="52" ht="15.75" customHeight="1" s="6"/>
-    <row r="53" ht="15.75" customHeight="1" s="6"/>
-    <row r="54" ht="15.75" customHeight="1" s="6"/>
-    <row r="55" ht="15.75" customHeight="1" s="6"/>
-    <row r="56" ht="15.75" customHeight="1" s="6"/>
-    <row r="57" ht="15.75" customHeight="1" s="6"/>
-    <row r="58" ht="15.75" customHeight="1" s="6"/>
-    <row r="59" ht="15.75" customHeight="1" s="6"/>
-    <row r="60" ht="15.75" customHeight="1" s="6"/>
-    <row r="61" ht="15.75" customHeight="1" s="6"/>
-    <row r="62" ht="15.75" customHeight="1" s="6"/>
-    <row r="63" ht="15.75" customHeight="1" s="6"/>
-    <row r="64" ht="15.75" customHeight="1" s="6"/>
-    <row r="65" ht="15.75" customHeight="1" s="6"/>
-    <row r="66" ht="15.75" customHeight="1" s="6"/>
-    <row r="67" ht="15.75" customHeight="1" s="6"/>
-    <row r="68" ht="15.75" customHeight="1" s="6"/>
-    <row r="69" ht="15.75" customHeight="1" s="6"/>
-    <row r="70" ht="15.75" customHeight="1" s="6"/>
-    <row r="71" ht="15.75" customHeight="1" s="6"/>
-    <row r="72" ht="15.75" customHeight="1" s="6"/>
-    <row r="73" ht="15.75" customHeight="1" s="6"/>
-    <row r="74" ht="15.75" customHeight="1" s="6"/>
-    <row r="75" ht="15.75" customHeight="1" s="6"/>
-    <row r="76" ht="15.75" customHeight="1" s="6"/>
-    <row r="77" ht="15.75" customHeight="1" s="6"/>
-    <row r="78" ht="15.75" customHeight="1" s="6"/>
-    <row r="79" ht="15.75" customHeight="1" s="6"/>
-    <row r="80" ht="15.75" customHeight="1" s="6"/>
-    <row r="81" ht="15.75" customHeight="1" s="6"/>
-    <row r="82" ht="15.75" customHeight="1" s="6"/>
-    <row r="83" ht="15.75" customHeight="1" s="6"/>
-    <row r="84" ht="15.75" customHeight="1" s="6"/>
-    <row r="85" ht="15.75" customHeight="1" s="6"/>
-    <row r="86" ht="15.75" customHeight="1" s="6"/>
-    <row r="87" ht="15.75" customHeight="1" s="6"/>
-    <row r="88" ht="15.75" customHeight="1" s="6"/>
-    <row r="89" ht="15.75" customHeight="1" s="6"/>
-    <row r="90" ht="15.75" customHeight="1" s="6"/>
-    <row r="91" ht="15.75" customHeight="1" s="6"/>
-    <row r="92" ht="15.75" customHeight="1" s="6"/>
-    <row r="93" ht="15.75" customHeight="1" s="6"/>
-    <row r="94" ht="15.75" customHeight="1" s="6"/>
-    <row r="95" ht="15.75" customHeight="1" s="6"/>
-    <row r="96" ht="15.75" customHeight="1" s="6"/>
-    <row r="97" ht="15.75" customHeight="1" s="6"/>
-    <row r="98" ht="15.75" customHeight="1" s="6"/>
-    <row r="99" ht="15.75" customHeight="1" s="6"/>
-    <row r="100" ht="15.75" customHeight="1" s="6"/>
-    <row r="101" ht="15.75" customHeight="1" s="6"/>
-    <row r="102" ht="15.75" customHeight="1" s="6"/>
-    <row r="103" ht="15.75" customHeight="1" s="6"/>
-    <row r="104" ht="15.75" customHeight="1" s="6"/>
-    <row r="105" ht="15.75" customHeight="1" s="6"/>
-    <row r="106" ht="15.75" customHeight="1" s="6"/>
-    <row r="107" ht="15.75" customHeight="1" s="6"/>
-    <row r="108" ht="15.75" customHeight="1" s="6"/>
-    <row r="109" ht="15.75" customHeight="1" s="6"/>
-    <row r="110" ht="15.75" customHeight="1" s="6"/>
-    <row r="111" ht="15.75" customHeight="1" s="6"/>
-    <row r="112" ht="15.75" customHeight="1" s="6"/>
-    <row r="113" ht="15.75" customHeight="1" s="6"/>
-    <row r="114" ht="15.75" customHeight="1" s="6"/>
-    <row r="115" ht="15.75" customHeight="1" s="6"/>
-    <row r="116" ht="15.75" customHeight="1" s="6"/>
-    <row r="117" ht="15.75" customHeight="1" s="6"/>
-    <row r="118" ht="15.75" customHeight="1" s="6"/>
-    <row r="119" ht="15.75" customHeight="1" s="6"/>
-    <row r="120" ht="15.75" customHeight="1" s="6"/>
-    <row r="121" ht="15.75" customHeight="1" s="6"/>
-    <row r="122" ht="15.75" customHeight="1" s="6"/>
-    <row r="123" ht="15.75" customHeight="1" s="6"/>
-    <row r="124" ht="15.75" customHeight="1" s="6"/>
-    <row r="125" ht="15.75" customHeight="1" s="6"/>
-    <row r="126" ht="15.75" customHeight="1" s="6"/>
-    <row r="127" ht="15.75" customHeight="1" s="6"/>
-    <row r="128" ht="15.75" customHeight="1" s="6"/>
-    <row r="129" ht="15.75" customHeight="1" s="6"/>
-    <row r="130" ht="15.75" customHeight="1" s="6"/>
-    <row r="131" ht="15.75" customHeight="1" s="6"/>
-    <row r="132" ht="15.75" customHeight="1" s="6"/>
-    <row r="133" ht="15.75" customHeight="1" s="6"/>
-    <row r="134" ht="15.75" customHeight="1" s="6"/>
-    <row r="135" ht="15.75" customHeight="1" s="6"/>
-    <row r="136" ht="15.75" customHeight="1" s="6"/>
-    <row r="137" ht="15.75" customHeight="1" s="6"/>
-    <row r="138" ht="15.75" customHeight="1" s="6"/>
-    <row r="139" ht="15.75" customHeight="1" s="6"/>
-    <row r="140" ht="15.75" customHeight="1" s="6"/>
-    <row r="141" ht="15.75" customHeight="1" s="6"/>
-    <row r="142" ht="15.75" customHeight="1" s="6"/>
-    <row r="143" ht="15.75" customHeight="1" s="6"/>
-    <row r="144" ht="15.75" customHeight="1" s="6"/>
-    <row r="145" ht="15.75" customHeight="1" s="6"/>
-    <row r="146" ht="15.75" customHeight="1" s="6"/>
-    <row r="147" ht="15.75" customHeight="1" s="6"/>
-    <row r="148" ht="15.75" customHeight="1" s="6"/>
-    <row r="149" ht="15.75" customHeight="1" s="6"/>
-    <row r="150" ht="15.75" customHeight="1" s="6"/>
-    <row r="151" ht="15.75" customHeight="1" s="6"/>
-    <row r="152" ht="15.75" customHeight="1" s="6"/>
-    <row r="153" ht="15.75" customHeight="1" s="6"/>
-    <row r="154" ht="15.75" customHeight="1" s="6"/>
-    <row r="155" ht="15.75" customHeight="1" s="6"/>
-    <row r="156" ht="15.75" customHeight="1" s="6"/>
-    <row r="157" ht="15.75" customHeight="1" s="6"/>
-    <row r="158" ht="15.75" customHeight="1" s="6"/>
-    <row r="159" ht="15.75" customHeight="1" s="6"/>
-    <row r="160" ht="15.75" customHeight="1" s="6"/>
-    <row r="161" ht="15.75" customHeight="1" s="6"/>
-    <row r="162" ht="15.75" customHeight="1" s="6"/>
-    <row r="163" ht="15.75" customHeight="1" s="6"/>
-    <row r="164" ht="15.75" customHeight="1" s="6"/>
-    <row r="165" ht="15.75" customHeight="1" s="6"/>
-    <row r="166" ht="15.75" customHeight="1" s="6"/>
-    <row r="167" ht="15.75" customHeight="1" s="6"/>
-    <row r="168" ht="15.75" customHeight="1" s="6"/>
-    <row r="169" ht="15.75" customHeight="1" s="6"/>
-    <row r="170" ht="15.75" customHeight="1" s="6"/>
-    <row r="171" ht="15.75" customHeight="1" s="6"/>
-    <row r="172" ht="15.75" customHeight="1" s="6"/>
-    <row r="173" ht="15.75" customHeight="1" s="6"/>
-    <row r="174" ht="15.75" customHeight="1" s="6"/>
-    <row r="175" ht="15.75" customHeight="1" s="6"/>
-    <row r="176" ht="15.75" customHeight="1" s="6"/>
-    <row r="177" ht="15.75" customHeight="1" s="6"/>
-    <row r="178" ht="15.75" customHeight="1" s="6"/>
-    <row r="179" ht="15.75" customHeight="1" s="6"/>
-    <row r="180" ht="15.75" customHeight="1" s="6"/>
-    <row r="181" ht="15.75" customHeight="1" s="6"/>
-    <row r="182" ht="15.75" customHeight="1" s="6"/>
-    <row r="183" ht="15.75" customHeight="1" s="6"/>
-    <row r="184" ht="15.75" customHeight="1" s="6"/>
-    <row r="185" ht="15.75" customHeight="1" s="6"/>
-    <row r="186" ht="15.75" customHeight="1" s="6"/>
-    <row r="187" ht="15.75" customHeight="1" s="6"/>
-    <row r="188" ht="15.75" customHeight="1" s="6"/>
-    <row r="189" ht="15.75" customHeight="1" s="6"/>
-    <row r="190" ht="15.75" customHeight="1" s="6"/>
-    <row r="191" ht="15.75" customHeight="1" s="6"/>
-    <row r="192" ht="15.75" customHeight="1" s="6"/>
-    <row r="193" ht="15.75" customHeight="1" s="6"/>
-    <row r="194" ht="15.75" customHeight="1" s="6"/>
-    <row r="195" ht="15.75" customHeight="1" s="6"/>
-    <row r="196" ht="15.75" customHeight="1" s="6"/>
-    <row r="197" ht="15.75" customHeight="1" s="6"/>
-    <row r="198" ht="15.75" customHeight="1" s="6"/>
-    <row r="199" ht="15.75" customHeight="1" s="6"/>
-    <row r="200" ht="15.75" customHeight="1" s="6"/>
-    <row r="201" ht="15.75" customHeight="1" s="6"/>
-    <row r="202" ht="15.75" customHeight="1" s="6"/>
-    <row r="203" ht="15.75" customHeight="1" s="6"/>
-    <row r="204" ht="15.75" customHeight="1" s="6"/>
-    <row r="205" ht="15.75" customHeight="1" s="6"/>
-    <row r="206" ht="15.75" customHeight="1" s="6"/>
-    <row r="207" ht="15.75" customHeight="1" s="6"/>
-    <row r="208" ht="15.75" customHeight="1" s="6"/>
-    <row r="209" ht="15.75" customHeight="1" s="6"/>
-    <row r="210" ht="15.75" customHeight="1" s="6"/>
-    <row r="211" ht="15.75" customHeight="1" s="6"/>
-    <row r="212" ht="15.75" customHeight="1" s="6"/>
-    <row r="213" ht="15.75" customHeight="1" s="6"/>
-    <row r="214" ht="15.75" customHeight="1" s="6"/>
-    <row r="215" ht="15.75" customHeight="1" s="6"/>
-    <row r="216" ht="15.75" customHeight="1" s="6"/>
-    <row r="217" ht="15.75" customHeight="1" s="6"/>
-    <row r="218" ht="15.75" customHeight="1" s="6"/>
-    <row r="219" ht="15.75" customHeight="1" s="6"/>
-    <row r="220" ht="15.75" customHeight="1" s="6"/>
-    <row r="221" ht="15.75" customHeight="1" s="6"/>
-    <row r="222" ht="15.75" customHeight="1" s="6"/>
-    <row r="223" ht="15.75" customHeight="1" s="6"/>
-    <row r="224" ht="15.75" customHeight="1" s="6"/>
-    <row r="225" ht="15.75" customHeight="1" s="6"/>
-    <row r="226" ht="15.75" customHeight="1" s="6"/>
-    <row r="227" ht="15.75" customHeight="1" s="6"/>
-    <row r="228" ht="15.75" customHeight="1" s="6"/>
-    <row r="229" ht="15.75" customHeight="1" s="6"/>
-    <row r="230" ht="15.75" customHeight="1" s="6"/>
-    <row r="231" ht="15.75" customHeight="1" s="6"/>
-    <row r="232" ht="15.75" customHeight="1" s="6"/>
-    <row r="233" ht="15.75" customHeight="1" s="6"/>
-    <row r="234" ht="15.75" customHeight="1" s="6"/>
-    <row r="235" ht="15.75" customHeight="1" s="6"/>
-    <row r="236" ht="15.75" customHeight="1" s="6"/>
-    <row r="237" ht="15.75" customHeight="1" s="6"/>
-    <row r="238" ht="15.75" customHeight="1" s="6"/>
-    <row r="239" ht="15.75" customHeight="1" s="6"/>
-    <row r="240" ht="15.75" customHeight="1" s="6"/>
-    <row r="241" ht="15.75" customHeight="1" s="6"/>
-    <row r="242" ht="15.75" customHeight="1" s="6"/>
-    <row r="243" ht="15.75" customHeight="1" s="6"/>
-    <row r="244" ht="15.75" customHeight="1" s="6"/>
-    <row r="245" ht="15.75" customHeight="1" s="6"/>
-    <row r="246" ht="15.75" customHeight="1" s="6"/>
-    <row r="247" ht="15.75" customHeight="1" s="6"/>
-    <row r="248" ht="15.75" customHeight="1" s="6"/>
-    <row r="249" ht="15.75" customHeight="1" s="6"/>
-    <row r="250" ht="15.75" customHeight="1" s="6"/>
-    <row r="251" ht="15.75" customHeight="1" s="6"/>
-    <row r="252" ht="15.75" customHeight="1" s="6"/>
-    <row r="253" ht="15.75" customHeight="1" s="6"/>
-    <row r="254" ht="15.75" customHeight="1" s="6"/>
-    <row r="255" ht="15.75" customHeight="1" s="6"/>
-    <row r="256" ht="15.75" customHeight="1" s="6"/>
-    <row r="257" ht="15.75" customHeight="1" s="6"/>
-    <row r="258" ht="15.75" customHeight="1" s="6"/>
-    <row r="259" ht="15.75" customHeight="1" s="6"/>
-    <row r="260" ht="15.75" customHeight="1" s="6"/>
-    <row r="261" ht="15.75" customHeight="1" s="6"/>
-    <row r="262" ht="15.75" customHeight="1" s="6"/>
-    <row r="263" ht="15.75" customHeight="1" s="6"/>
-    <row r="264" ht="15.75" customHeight="1" s="6"/>
-    <row r="265" ht="15.75" customHeight="1" s="6"/>
-    <row r="266" ht="15.75" customHeight="1" s="6"/>
-    <row r="267" ht="15.75" customHeight="1" s="6"/>
-    <row r="268" ht="15.75" customHeight="1" s="6"/>
-    <row r="269" ht="15.75" customHeight="1" s="6"/>
-    <row r="270" ht="15.75" customHeight="1" s="6"/>
-    <row r="271" ht="15.75" customHeight="1" s="6"/>
-    <row r="272" ht="15.75" customHeight="1" s="6"/>
-    <row r="273" ht="15.75" customHeight="1" s="6"/>
-    <row r="274" ht="15.75" customHeight="1" s="6"/>
-    <row r="275" ht="15.75" customHeight="1" s="6"/>
-    <row r="276" ht="15.75" customHeight="1" s="6"/>
-    <row r="277" ht="15.75" customHeight="1" s="6"/>
-    <row r="278" ht="15.75" customHeight="1" s="6"/>
-    <row r="279" ht="15.75" customHeight="1" s="6"/>
-    <row r="280" ht="15.75" customHeight="1" s="6"/>
-    <row r="281" ht="15.75" customHeight="1" s="6"/>
-    <row r="282" ht="15.75" customHeight="1" s="6"/>
-    <row r="283" ht="15.75" customHeight="1" s="6"/>
-    <row r="284" ht="15.75" customHeight="1" s="6"/>
-    <row r="285" ht="15.75" customHeight="1" s="6"/>
-    <row r="286" ht="15.75" customHeight="1" s="6"/>
-    <row r="287" ht="15.75" customHeight="1" s="6"/>
-    <row r="288" ht="15.75" customHeight="1" s="6"/>
-    <row r="289" ht="15.75" customHeight="1" s="6"/>
-    <row r="290" ht="15.75" customHeight="1" s="6"/>
-    <row r="291" ht="15.75" customHeight="1" s="6"/>
-    <row r="292" ht="15.75" customHeight="1" s="6"/>
-    <row r="293" ht="15.75" customHeight="1" s="6"/>
-    <row r="294" ht="15.75" customHeight="1" s="6"/>
-    <row r="295" ht="15.75" customHeight="1" s="6"/>
-    <row r="296" ht="15.75" customHeight="1" s="6"/>
-    <row r="297" ht="15.75" customHeight="1" s="6"/>
-    <row r="298" ht="15.75" customHeight="1" s="6"/>
-    <row r="299" ht="15.75" customHeight="1" s="6"/>
-    <row r="300" ht="15.75" customHeight="1" s="6"/>
-    <row r="301" ht="15.75" customHeight="1" s="6"/>
-    <row r="302" ht="15.75" customHeight="1" s="6"/>
-    <row r="303" ht="15.75" customHeight="1" s="6"/>
-    <row r="304" ht="15.75" customHeight="1" s="6"/>
-    <row r="305" ht="15.75" customHeight="1" s="6"/>
-    <row r="306" ht="15.75" customHeight="1" s="6"/>
-    <row r="307" ht="15.75" customHeight="1" s="6"/>
-    <row r="308" ht="15.75" customHeight="1" s="6"/>
-    <row r="309" ht="15.75" customHeight="1" s="6"/>
-    <row r="310" ht="15.75" customHeight="1" s="6"/>
-    <row r="311" ht="15.75" customHeight="1" s="6"/>
-    <row r="312" ht="15.75" customHeight="1" s="6"/>
-    <row r="313" ht="15.75" customHeight="1" s="6"/>
-    <row r="314" ht="15.75" customHeight="1" s="6"/>
-    <row r="315" ht="15.75" customHeight="1" s="6"/>
-    <row r="316" ht="15.75" customHeight="1" s="6"/>
-    <row r="317" ht="15.75" customHeight="1" s="6"/>
-    <row r="318" ht="15.75" customHeight="1" s="6"/>
-    <row r="319" ht="15.75" customHeight="1" s="6"/>
-    <row r="320" ht="15.75" customHeight="1" s="6"/>
-    <row r="321" ht="15.75" customHeight="1" s="6"/>
-    <row r="322" ht="15.75" customHeight="1" s="6"/>
-    <row r="323" ht="15.75" customHeight="1" s="6"/>
-    <row r="324" ht="15.75" customHeight="1" s="6"/>
-    <row r="325" ht="15.75" customHeight="1" s="6"/>
-    <row r="326" ht="15.75" customHeight="1" s="6"/>
-    <row r="327" ht="15.75" customHeight="1" s="6"/>
-    <row r="328" ht="15.75" customHeight="1" s="6"/>
-    <row r="329" ht="15.75" customHeight="1" s="6"/>
-    <row r="330" ht="15.75" customHeight="1" s="6"/>
-    <row r="331" ht="15.75" customHeight="1" s="6"/>
-    <row r="332" ht="15.75" customHeight="1" s="6"/>
-    <row r="333" ht="15.75" customHeight="1" s="6"/>
-    <row r="334" ht="15.75" customHeight="1" s="6"/>
-    <row r="335" ht="15.75" customHeight="1" s="6"/>
-    <row r="336" ht="15.75" customHeight="1" s="6"/>
-    <row r="337" ht="15.75" customHeight="1" s="6"/>
-    <row r="338" ht="15.75" customHeight="1" s="6"/>
-    <row r="339" ht="15.75" customHeight="1" s="6"/>
-    <row r="340" ht="15.75" customHeight="1" s="6"/>
-    <row r="341" ht="15.75" customHeight="1" s="6"/>
-    <row r="342" ht="15.75" customHeight="1" s="6"/>
-    <row r="343" ht="15.75" customHeight="1" s="6"/>
-    <row r="344" ht="15.75" customHeight="1" s="6"/>
-    <row r="345" ht="15.75" customHeight="1" s="6"/>
-    <row r="346" ht="15.75" customHeight="1" s="6"/>
-    <row r="347" ht="15.75" customHeight="1" s="6"/>
-    <row r="348" ht="15.75" customHeight="1" s="6"/>
-    <row r="349" ht="15.75" customHeight="1" s="6"/>
-    <row r="350" ht="15.75" customHeight="1" s="6"/>
-    <row r="351" ht="15.75" customHeight="1" s="6"/>
-    <row r="352" ht="15.75" customHeight="1" s="6"/>
-    <row r="353" ht="15.75" customHeight="1" s="6"/>
-    <row r="354" ht="15.75" customHeight="1" s="6"/>
-    <row r="355" ht="15.75" customHeight="1" s="6"/>
-    <row r="356" ht="15.75" customHeight="1" s="6"/>
-    <row r="357" ht="15.75" customHeight="1" s="6"/>
-    <row r="358" ht="15.75" customHeight="1" s="6"/>
-    <row r="359" ht="15.75" customHeight="1" s="6"/>
-    <row r="360" ht="15.75" customHeight="1" s="6"/>
-    <row r="361" ht="15.75" customHeight="1" s="6"/>
-    <row r="362" ht="15.75" customHeight="1" s="6"/>
-    <row r="363" ht="15.75" customHeight="1" s="6"/>
-    <row r="364" ht="15.75" customHeight="1" s="6"/>
-    <row r="365" ht="15.75" customHeight="1" s="6"/>
-    <row r="366" ht="15.75" customHeight="1" s="6"/>
-    <row r="367" ht="15.75" customHeight="1" s="6"/>
-    <row r="368" ht="15.75" customHeight="1" s="6"/>
-    <row r="369" ht="15.75" customHeight="1" s="6"/>
-    <row r="370" ht="15.75" customHeight="1" s="6"/>
-    <row r="371" ht="15.75" customHeight="1" s="6"/>
-    <row r="372" ht="15.75" customHeight="1" s="6"/>
-    <row r="373" ht="15.75" customHeight="1" s="6"/>
-    <row r="374" ht="15.75" customHeight="1" s="6"/>
-    <row r="375" ht="15.75" customHeight="1" s="6"/>
-    <row r="376" ht="15.75" customHeight="1" s="6"/>
-    <row r="377" ht="15.75" customHeight="1" s="6"/>
-    <row r="378" ht="15.75" customHeight="1" s="6"/>
-    <row r="379" ht="15.75" customHeight="1" s="6"/>
-    <row r="380" ht="15.75" customHeight="1" s="6"/>
-    <row r="381" ht="15.75" customHeight="1" s="6"/>
-    <row r="382" ht="15.75" customHeight="1" s="6"/>
-    <row r="383" ht="15.75" customHeight="1" s="6"/>
-    <row r="384" ht="15.75" customHeight="1" s="6"/>
-    <row r="385" ht="15.75" customHeight="1" s="6"/>
-    <row r="386" ht="15.75" customHeight="1" s="6"/>
-    <row r="387" ht="15.75" customHeight="1" s="6"/>
-    <row r="388" ht="15.75" customHeight="1" s="6"/>
-    <row r="389" ht="15.75" customHeight="1" s="6"/>
-    <row r="390" ht="15.75" customHeight="1" s="6"/>
-    <row r="391" ht="15.75" customHeight="1" s="6"/>
-    <row r="392" ht="15.75" customHeight="1" s="6"/>
-    <row r="393" ht="15.75" customHeight="1" s="6"/>
-    <row r="394" ht="15.75" customHeight="1" s="6"/>
-    <row r="395" ht="15.75" customHeight="1" s="6"/>
-    <row r="396" ht="15.75" customHeight="1" s="6"/>
-    <row r="397" ht="15.75" customHeight="1" s="6"/>
-    <row r="398" ht="15.75" customHeight="1" s="6"/>
-    <row r="399" ht="15.75" customHeight="1" s="6"/>
-    <row r="400" ht="15.75" customHeight="1" s="6"/>
-    <row r="401" ht="15.75" customHeight="1" s="6"/>
-    <row r="402" ht="15.75" customHeight="1" s="6"/>
-    <row r="403" ht="15.75" customHeight="1" s="6"/>
-    <row r="404" ht="15.75" customHeight="1" s="6"/>
-    <row r="405" ht="15.75" customHeight="1" s="6"/>
-    <row r="406" ht="15.75" customHeight="1" s="6"/>
-    <row r="407" ht="15.75" customHeight="1" s="6"/>
-    <row r="408" ht="15.75" customHeight="1" s="6"/>
-    <row r="409" ht="15.75" customHeight="1" s="6"/>
-    <row r="410" ht="15.75" customHeight="1" s="6"/>
-    <row r="411" ht="15.75" customHeight="1" s="6"/>
-    <row r="412" ht="15.75" customHeight="1" s="6"/>
-    <row r="413" ht="15.75" customHeight="1" s="6"/>
-    <row r="414" ht="15.75" customHeight="1" s="6"/>
-    <row r="415" ht="15.75" customHeight="1" s="6"/>
-    <row r="416" ht="15.75" customHeight="1" s="6"/>
-    <row r="417" ht="15.75" customHeight="1" s="6"/>
-    <row r="418" ht="15.75" customHeight="1" s="6"/>
-    <row r="419" ht="15.75" customHeight="1" s="6"/>
-    <row r="420" ht="15.75" customHeight="1" s="6"/>
-    <row r="421" ht="15.75" customHeight="1" s="6"/>
-    <row r="422" ht="15.75" customHeight="1" s="6"/>
-    <row r="423" ht="15.75" customHeight="1" s="6"/>
-    <row r="424" ht="15.75" customHeight="1" s="6"/>
-    <row r="425" ht="15.75" customHeight="1" s="6"/>
-    <row r="426" ht="15.75" customHeight="1" s="6"/>
-    <row r="427" ht="15.75" customHeight="1" s="6"/>
-    <row r="428" ht="15.75" customHeight="1" s="6"/>
-    <row r="429" ht="15.75" customHeight="1" s="6"/>
-    <row r="430" ht="15.75" customHeight="1" s="6"/>
-    <row r="431" ht="15.75" customHeight="1" s="6"/>
-    <row r="432" ht="15.75" customHeight="1" s="6"/>
-    <row r="433" ht="15.75" customHeight="1" s="6"/>
-    <row r="434" ht="15.75" customHeight="1" s="6"/>
-    <row r="435" ht="15.75" customHeight="1" s="6"/>
-    <row r="436" ht="15.75" customHeight="1" s="6"/>
-    <row r="437" ht="15.75" customHeight="1" s="6"/>
-    <row r="438" ht="15.75" customHeight="1" s="6"/>
-    <row r="439" ht="15.75" customHeight="1" s="6"/>
-    <row r="440" ht="15.75" customHeight="1" s="6"/>
-    <row r="441" ht="15.75" customHeight="1" s="6"/>
-    <row r="442" ht="15.75" customHeight="1" s="6"/>
-    <row r="443" ht="15.75" customHeight="1" s="6"/>
-    <row r="444" ht="15.75" customHeight="1" s="6"/>
-    <row r="445" ht="15.75" customHeight="1" s="6"/>
-    <row r="446" ht="15.75" customHeight="1" s="6"/>
-    <row r="447" ht="15.75" customHeight="1" s="6"/>
-    <row r="448" ht="15.75" customHeight="1" s="6"/>
-    <row r="449" ht="15.75" customHeight="1" s="6"/>
-    <row r="450" ht="15.75" customHeight="1" s="6"/>
-    <row r="451" ht="15.75" customHeight="1" s="6"/>
-    <row r="452" ht="15.75" customHeight="1" s="6"/>
-    <row r="453" ht="15.75" customHeight="1" s="6"/>
-    <row r="454" ht="15.75" customHeight="1" s="6"/>
-    <row r="455" ht="15.75" customHeight="1" s="6"/>
-    <row r="456" ht="15.75" customHeight="1" s="6"/>
-    <row r="457" ht="15.75" customHeight="1" s="6"/>
-    <row r="458" ht="15.75" customHeight="1" s="6"/>
-    <row r="459" ht="15.75" customHeight="1" s="6"/>
-    <row r="460" ht="15.75" customHeight="1" s="6"/>
-    <row r="461" ht="15.75" customHeight="1" s="6"/>
-    <row r="462" ht="15.75" customHeight="1" s="6"/>
-    <row r="463" ht="15.75" customHeight="1" s="6"/>
-    <row r="464" ht="15.75" customHeight="1" s="6"/>
-    <row r="465" ht="15.75" customHeight="1" s="6"/>
-    <row r="466" ht="15.75" customHeight="1" s="6"/>
-    <row r="467" ht="15.75" customHeight="1" s="6"/>
-    <row r="468" ht="15.75" customHeight="1" s="6"/>
-    <row r="469" ht="15.75" customHeight="1" s="6"/>
-    <row r="470" ht="15.75" customHeight="1" s="6"/>
-    <row r="471" ht="15.75" customHeight="1" s="6"/>
-    <row r="472" ht="15.75" customHeight="1" s="6"/>
-    <row r="473" ht="15.75" customHeight="1" s="6"/>
-    <row r="474" ht="15.75" customHeight="1" s="6"/>
-    <row r="475" ht="15.75" customHeight="1" s="6"/>
-    <row r="476" ht="15.75" customHeight="1" s="6"/>
-    <row r="477" ht="15.75" customHeight="1" s="6"/>
-    <row r="478" ht="15.75" customHeight="1" s="6"/>
-    <row r="479" ht="15.75" customHeight="1" s="6"/>
-    <row r="480" ht="15.75" customHeight="1" s="6"/>
-    <row r="481" ht="15.75" customHeight="1" s="6"/>
-    <row r="482" ht="15.75" customHeight="1" s="6"/>
-    <row r="483" ht="15.75" customHeight="1" s="6"/>
-    <row r="484" ht="15.75" customHeight="1" s="6"/>
-    <row r="485" ht="15.75" customHeight="1" s="6"/>
-    <row r="486" ht="15.75" customHeight="1" s="6"/>
-    <row r="487" ht="15.75" customHeight="1" s="6"/>
-    <row r="488" ht="15.75" customHeight="1" s="6"/>
-    <row r="489" ht="15.75" customHeight="1" s="6"/>
-    <row r="490" ht="15.75" customHeight="1" s="6"/>
-    <row r="491" ht="15.75" customHeight="1" s="6"/>
-    <row r="492" ht="15.75" customHeight="1" s="6"/>
-    <row r="493" ht="15.75" customHeight="1" s="6"/>
-    <row r="494" ht="15.75" customHeight="1" s="6"/>
-    <row r="495" ht="15.75" customHeight="1" s="6"/>
-    <row r="496" ht="15.75" customHeight="1" s="6"/>
-    <row r="497" ht="15.75" customHeight="1" s="6"/>
-    <row r="498" ht="15.75" customHeight="1" s="6"/>
-    <row r="499" ht="15.75" customHeight="1" s="6"/>
-    <row r="500" ht="15.75" customHeight="1" s="6"/>
-    <row r="501" ht="15.75" customHeight="1" s="6"/>
-    <row r="502" ht="15.75" customHeight="1" s="6"/>
-    <row r="503" ht="15.75" customHeight="1" s="6"/>
-    <row r="504" ht="15.75" customHeight="1" s="6"/>
-    <row r="505" ht="15.75" customHeight="1" s="6"/>
-    <row r="506" ht="15.75" customHeight="1" s="6"/>
-    <row r="507" ht="15.75" customHeight="1" s="6"/>
-    <row r="508" ht="15.75" customHeight="1" s="6"/>
-    <row r="509" ht="15.75" customHeight="1" s="6"/>
-    <row r="510" ht="15.75" customHeight="1" s="6"/>
-    <row r="511" ht="15.75" customHeight="1" s="6"/>
-    <row r="512" ht="15.75" customHeight="1" s="6"/>
-    <row r="513" ht="15.75" customHeight="1" s="6"/>
-    <row r="514" ht="15.75" customHeight="1" s="6"/>
-    <row r="515" ht="15.75" customHeight="1" s="6"/>
-    <row r="516" ht="15.75" customHeight="1" s="6"/>
-    <row r="517" ht="15.75" customHeight="1" s="6"/>
-    <row r="518" ht="15.75" customHeight="1" s="6"/>
-    <row r="519" ht="15.75" customHeight="1" s="6"/>
-    <row r="520" ht="15.75" customHeight="1" s="6"/>
-    <row r="521" ht="15.75" customHeight="1" s="6"/>
-    <row r="522" ht="15.75" customHeight="1" s="6"/>
-    <row r="523" ht="15.75" customHeight="1" s="6"/>
-    <row r="524" ht="15.75" customHeight="1" s="6"/>
-    <row r="525" ht="15.75" customHeight="1" s="6"/>
-    <row r="526" ht="15.75" customHeight="1" s="6"/>
-    <row r="527" ht="15.75" customHeight="1" s="6"/>
-    <row r="528" ht="15.75" customHeight="1" s="6"/>
-    <row r="529" ht="15.75" customHeight="1" s="6"/>
-    <row r="530" ht="15.75" customHeight="1" s="6"/>
-    <row r="531" ht="15.75" customHeight="1" s="6"/>
-    <row r="532" ht="15.75" customHeight="1" s="6"/>
-    <row r="533" ht="15.75" customHeight="1" s="6"/>
-    <row r="534" ht="15.75" customHeight="1" s="6"/>
-    <row r="535" ht="15.75" customHeight="1" s="6"/>
-    <row r="536" ht="15.75" customHeight="1" s="6"/>
-    <row r="537" ht="15.75" customHeight="1" s="6"/>
-    <row r="538" ht="15.75" customHeight="1" s="6"/>
-    <row r="539" ht="15.75" customHeight="1" s="6"/>
-    <row r="540" ht="15.75" customHeight="1" s="6"/>
-    <row r="541" ht="15.75" customHeight="1" s="6"/>
-    <row r="542" ht="15.75" customHeight="1" s="6"/>
-    <row r="543" ht="15.75" customHeight="1" s="6"/>
-    <row r="544" ht="15.75" customHeight="1" s="6"/>
-    <row r="545" ht="15.75" customHeight="1" s="6"/>
-    <row r="546" ht="15.75" customHeight="1" s="6"/>
-    <row r="547" ht="15.75" customHeight="1" s="6"/>
-    <row r="548" ht="15.75" customHeight="1" s="6"/>
-    <row r="549" ht="15.75" customHeight="1" s="6"/>
-    <row r="550" ht="15.75" customHeight="1" s="6"/>
-    <row r="551" ht="15.75" customHeight="1" s="6"/>
-    <row r="552" ht="15.75" customHeight="1" s="6"/>
-    <row r="553" ht="15.75" customHeight="1" s="6"/>
-    <row r="554" ht="15.75" customHeight="1" s="6"/>
-    <row r="555" ht="15.75" customHeight="1" s="6"/>
-    <row r="556" ht="15.75" customHeight="1" s="6"/>
-    <row r="557" ht="15.75" customHeight="1" s="6"/>
-    <row r="558" ht="15.75" customHeight="1" s="6"/>
-    <row r="559" ht="15.75" customHeight="1" s="6"/>
-    <row r="560" ht="15.75" customHeight="1" s="6"/>
-    <row r="561" ht="15.75" customHeight="1" s="6"/>
-    <row r="562" ht="15.75" customHeight="1" s="6"/>
-    <row r="563" ht="15.75" customHeight="1" s="6"/>
-    <row r="564" ht="15.75" customHeight="1" s="6"/>
-    <row r="565" ht="15.75" customHeight="1" s="6"/>
-    <row r="566" ht="15.75" customHeight="1" s="6"/>
-    <row r="567" ht="15.75" customHeight="1" s="6"/>
-    <row r="568" ht="15.75" customHeight="1" s="6"/>
-    <row r="569" ht="15.75" customHeight="1" s="6"/>
-    <row r="570" ht="15.75" customHeight="1" s="6"/>
-    <row r="571" ht="15.75" customHeight="1" s="6"/>
-    <row r="572" ht="15.75" customHeight="1" s="6"/>
-    <row r="573" ht="15.75" customHeight="1" s="6"/>
-    <row r="574" ht="15.75" customHeight="1" s="6"/>
-    <row r="575" ht="15.75" customHeight="1" s="6"/>
-    <row r="576" ht="15.75" customHeight="1" s="6"/>
-    <row r="577" ht="15.75" customHeight="1" s="6"/>
-    <row r="578" ht="15.75" customHeight="1" s="6"/>
-    <row r="579" ht="15.75" customHeight="1" s="6"/>
-    <row r="580" ht="15.75" customHeight="1" s="6"/>
-    <row r="581" ht="15.75" customHeight="1" s="6"/>
-    <row r="582" ht="15.75" customHeight="1" s="6"/>
-    <row r="583" ht="15.75" customHeight="1" s="6"/>
-    <row r="584" ht="15.75" customHeight="1" s="6"/>
-    <row r="585" ht="15.75" customHeight="1" s="6"/>
-    <row r="586" ht="15.75" customHeight="1" s="6"/>
-    <row r="587" ht="15.75" customHeight="1" s="6"/>
-    <row r="588" ht="15.75" customHeight="1" s="6"/>
-    <row r="589" ht="15.75" customHeight="1" s="6"/>
-    <row r="590" ht="15.75" customHeight="1" s="6"/>
-    <row r="591" ht="15.75" customHeight="1" s="6"/>
-    <row r="592" ht="15.75" customHeight="1" s="6"/>
-    <row r="593" ht="15.75" customHeight="1" s="6"/>
-    <row r="594" ht="15.75" customHeight="1" s="6"/>
-    <row r="595" ht="15.75" customHeight="1" s="6"/>
-    <row r="596" ht="15.75" customHeight="1" s="6"/>
-    <row r="597" ht="15.75" customHeight="1" s="6"/>
-    <row r="598" ht="15.75" customHeight="1" s="6"/>
-    <row r="599" ht="15.75" customHeight="1" s="6"/>
-    <row r="600" ht="15.75" customHeight="1" s="6"/>
-    <row r="601" ht="15.75" customHeight="1" s="6"/>
-    <row r="602" ht="15.75" customHeight="1" s="6"/>
-    <row r="603" ht="15.75" customHeight="1" s="6"/>
-    <row r="604" ht="15.75" customHeight="1" s="6"/>
-    <row r="605" ht="15.75" customHeight="1" s="6"/>
-    <row r="606" ht="15.75" customHeight="1" s="6"/>
-    <row r="607" ht="15.75" customHeight="1" s="6"/>
-    <row r="608" ht="15.75" customHeight="1" s="6"/>
-    <row r="609" ht="15.75" customHeight="1" s="6"/>
-    <row r="610" ht="15.75" customHeight="1" s="6"/>
-    <row r="611" ht="15.75" customHeight="1" s="6"/>
-    <row r="612" ht="15.75" customHeight="1" s="6"/>
-    <row r="613" ht="15.75" customHeight="1" s="6"/>
-    <row r="614" ht="15.75" customHeight="1" s="6"/>
-    <row r="615" ht="15.75" customHeight="1" s="6"/>
-    <row r="616" ht="15.75" customHeight="1" s="6"/>
-    <row r="617" ht="15.75" customHeight="1" s="6"/>
-    <row r="618" ht="15.75" customHeight="1" s="6"/>
-    <row r="619" ht="15.75" customHeight="1" s="6"/>
-    <row r="620" ht="15.75" customHeight="1" s="6"/>
-    <row r="621" ht="15.75" customHeight="1" s="6"/>
-    <row r="622" ht="15.75" customHeight="1" s="6"/>
-    <row r="623" ht="15.75" customHeight="1" s="6"/>
-    <row r="624" ht="15.75" customHeight="1" s="6"/>
-    <row r="625" ht="15.75" customHeight="1" s="6"/>
-    <row r="626" ht="15.75" customHeight="1" s="6"/>
-    <row r="627" ht="15.75" customHeight="1" s="6"/>
-    <row r="628" ht="15.75" customHeight="1" s="6"/>
-    <row r="629" ht="15.75" customHeight="1" s="6"/>
-    <row r="630" ht="15.75" customHeight="1" s="6"/>
-    <row r="631" ht="15.75" customHeight="1" s="6"/>
-    <row r="632" ht="15.75" customHeight="1" s="6"/>
-    <row r="633" ht="15.75" customHeight="1" s="6"/>
-    <row r="634" ht="15.75" customHeight="1" s="6"/>
-    <row r="635" ht="15.75" customHeight="1" s="6"/>
-    <row r="636" ht="15.75" customHeight="1" s="6"/>
-    <row r="637" ht="15.75" customHeight="1" s="6"/>
-    <row r="638" ht="15.75" customHeight="1" s="6"/>
-    <row r="639" ht="15.75" customHeight="1" s="6"/>
-    <row r="640" ht="15.75" customHeight="1" s="6"/>
-    <row r="641" ht="15.75" customHeight="1" s="6"/>
-    <row r="642" ht="15.75" customHeight="1" s="6"/>
-    <row r="643" ht="15.75" customHeight="1" s="6"/>
-    <row r="644" ht="15.75" customHeight="1" s="6"/>
-    <row r="645" ht="15.75" customHeight="1" s="6"/>
-    <row r="646" ht="15.75" customHeight="1" s="6"/>
-    <row r="647" ht="15.75" customHeight="1" s="6"/>
-    <row r="648" ht="15.75" customHeight="1" s="6"/>
-    <row r="649" ht="15.75" customHeight="1" s="6"/>
-    <row r="650" ht="15.75" customHeight="1" s="6"/>
-    <row r="651" ht="15.75" customHeight="1" s="6"/>
-    <row r="652" ht="15.75" customHeight="1" s="6"/>
-    <row r="653" ht="15.75" customHeight="1" s="6"/>
-    <row r="654" ht="15.75" customHeight="1" s="6"/>
-    <row r="655" ht="15.75" customHeight="1" s="6"/>
-    <row r="656" ht="15.75" customHeight="1" s="6"/>
-    <row r="657" ht="15.75" customHeight="1" s="6"/>
-    <row r="658" ht="15.75" customHeight="1" s="6"/>
-    <row r="659" ht="15.75" customHeight="1" s="6"/>
-    <row r="660" ht="15.75" customHeight="1" s="6"/>
-    <row r="661" ht="15.75" customHeight="1" s="6"/>
-    <row r="662" ht="15.75" customHeight="1" s="6"/>
-    <row r="663" ht="15.75" customHeight="1" s="6"/>
-    <row r="664" ht="15.75" customHeight="1" s="6"/>
-    <row r="665" ht="15.75" customHeight="1" s="6"/>
-    <row r="666" ht="15.75" customHeight="1" s="6"/>
-    <row r="667" ht="15.75" customHeight="1" s="6"/>
-    <row r="668" ht="15.75" customHeight="1" s="6"/>
-    <row r="669" ht="15.75" customHeight="1" s="6"/>
-    <row r="670" ht="15.75" customHeight="1" s="6"/>
-    <row r="671" ht="15.75" customHeight="1" s="6"/>
-    <row r="672" ht="15.75" customHeight="1" s="6"/>
-    <row r="673" ht="15.75" customHeight="1" s="6"/>
-    <row r="674" ht="15.75" customHeight="1" s="6"/>
-    <row r="675" ht="15.75" customHeight="1" s="6"/>
-    <row r="676" ht="15.75" customHeight="1" s="6"/>
-    <row r="677" ht="15.75" customHeight="1" s="6"/>
-    <row r="678" ht="15.75" customHeight="1" s="6"/>
-    <row r="679" ht="15.75" customHeight="1" s="6"/>
-    <row r="680" ht="15.75" customHeight="1" s="6"/>
-    <row r="681" ht="15.75" customHeight="1" s="6"/>
-    <row r="682" ht="15.75" customHeight="1" s="6"/>
-    <row r="683" ht="15.75" customHeight="1" s="6"/>
-    <row r="684" ht="15.75" customHeight="1" s="6"/>
-    <row r="685" ht="15.75" customHeight="1" s="6"/>
-    <row r="686" ht="15.75" customHeight="1" s="6"/>
-    <row r="687" ht="15.75" customHeight="1" s="6"/>
-    <row r="688" ht="15.75" customHeight="1" s="6"/>
-    <row r="689" ht="15.75" customHeight="1" s="6"/>
-    <row r="690" ht="15.75" customHeight="1" s="6"/>
-    <row r="691" ht="15.75" customHeight="1" s="6"/>
-    <row r="692" ht="15.75" customHeight="1" s="6"/>
-    <row r="693" ht="15.75" customHeight="1" s="6"/>
-    <row r="694" ht="15.75" customHeight="1" s="6"/>
-    <row r="695" ht="15.75" customHeight="1" s="6"/>
-    <row r="696" ht="15.75" customHeight="1" s="6"/>
-    <row r="697" ht="15.75" customHeight="1" s="6"/>
-    <row r="698" ht="15.75" customHeight="1" s="6"/>
-    <row r="699" ht="15.75" customHeight="1" s="6"/>
-    <row r="700" ht="15.75" customHeight="1" s="6"/>
-    <row r="701" ht="15.75" customHeight="1" s="6"/>
-    <row r="702" ht="15.75" customHeight="1" s="6"/>
-    <row r="703" ht="15.75" customHeight="1" s="6"/>
-    <row r="704" ht="15.75" customHeight="1" s="6"/>
-    <row r="705" ht="15.75" customHeight="1" s="6"/>
-    <row r="706" ht="15.75" customHeight="1" s="6"/>
-    <row r="707" ht="15.75" customHeight="1" s="6"/>
-    <row r="708" ht="15.75" customHeight="1" s="6"/>
-    <row r="709" ht="15.75" customHeight="1" s="6"/>
-    <row r="710" ht="15.75" customHeight="1" s="6"/>
-    <row r="711" ht="15.75" customHeight="1" s="6"/>
-    <row r="712" ht="15.75" customHeight="1" s="6"/>
-    <row r="713" ht="15.75" customHeight="1" s="6"/>
-    <row r="714" ht="15.75" customHeight="1" s="6"/>
-    <row r="715" ht="15.75" customHeight="1" s="6"/>
-    <row r="716" ht="15.75" customHeight="1" s="6"/>
-    <row r="717" ht="15.75" customHeight="1" s="6"/>
-    <row r="718" ht="15.75" customHeight="1" s="6"/>
-    <row r="719" ht="15.75" customHeight="1" s="6"/>
-    <row r="720" ht="15.75" customHeight="1" s="6"/>
-    <row r="721" ht="15.75" customHeight="1" s="6"/>
-    <row r="722" ht="15.75" customHeight="1" s="6"/>
-    <row r="723" ht="15.75" customHeight="1" s="6"/>
-    <row r="724" ht="15.75" customHeight="1" s="6"/>
-    <row r="725" ht="15.75" customHeight="1" s="6"/>
-    <row r="726" ht="15.75" customHeight="1" s="6"/>
-    <row r="727" ht="15.75" customHeight="1" s="6"/>
-    <row r="728" ht="15.75" customHeight="1" s="6"/>
-    <row r="729" ht="15.75" customHeight="1" s="6"/>
-    <row r="730" ht="15.75" customHeight="1" s="6"/>
-    <row r="731" ht="15.75" customHeight="1" s="6"/>
-    <row r="732" ht="15.75" customHeight="1" s="6"/>
-    <row r="733" ht="15.75" customHeight="1" s="6"/>
-    <row r="734" ht="15.75" customHeight="1" s="6"/>
-    <row r="735" ht="15.75" customHeight="1" s="6"/>
-    <row r="736" ht="15.75" customHeight="1" s="6"/>
-    <row r="737" ht="15.75" customHeight="1" s="6"/>
-    <row r="738" ht="15.75" customHeight="1" s="6"/>
-    <row r="739" ht="15.75" customHeight="1" s="6"/>
-    <row r="740" ht="15.75" customHeight="1" s="6"/>
-    <row r="741" ht="15.75" customHeight="1" s="6"/>
-    <row r="742" ht="15.75" customHeight="1" s="6"/>
-    <row r="743" ht="15.75" customHeight="1" s="6"/>
-    <row r="744" ht="15.75" customHeight="1" s="6"/>
-    <row r="745" ht="15.75" customHeight="1" s="6"/>
-    <row r="746" ht="15.75" customHeight="1" s="6"/>
-    <row r="747" ht="15.75" customHeight="1" s="6"/>
-    <row r="748" ht="15.75" customHeight="1" s="6"/>
-    <row r="749" ht="15.75" customHeight="1" s="6"/>
-    <row r="750" ht="15.75" customHeight="1" s="6"/>
-    <row r="751" ht="15.75" customHeight="1" s="6"/>
-    <row r="752" ht="15.75" customHeight="1" s="6"/>
-    <row r="753" ht="15.75" customHeight="1" s="6"/>
-    <row r="754" ht="15.75" customHeight="1" s="6"/>
-    <row r="755" ht="15.75" customHeight="1" s="6"/>
-    <row r="756" ht="15.75" customHeight="1" s="6"/>
-    <row r="757" ht="15.75" customHeight="1" s="6"/>
-    <row r="758" ht="15.75" customHeight="1" s="6"/>
-    <row r="759" ht="15.75" customHeight="1" s="6"/>
-    <row r="760" ht="15.75" customHeight="1" s="6"/>
-    <row r="761" ht="15.75" customHeight="1" s="6"/>
-    <row r="762" ht="15.75" customHeight="1" s="6"/>
-    <row r="763" ht="15.75" customHeight="1" s="6"/>
-    <row r="764" ht="15.75" customHeight="1" s="6"/>
-    <row r="765" ht="15.75" customHeight="1" s="6"/>
-    <row r="766" ht="15.75" customHeight="1" s="6"/>
-    <row r="767" ht="15.75" customHeight="1" s="6"/>
-    <row r="768" ht="15.75" customHeight="1" s="6"/>
-    <row r="769" ht="15.75" customHeight="1" s="6"/>
-    <row r="770" ht="15.75" customHeight="1" s="6"/>
-    <row r="771" ht="15.75" customHeight="1" s="6"/>
-    <row r="772" ht="15.75" customHeight="1" s="6"/>
-    <row r="773" ht="15.75" customHeight="1" s="6"/>
-    <row r="774" ht="15.75" customHeight="1" s="6"/>
-    <row r="775" ht="15.75" customHeight="1" s="6"/>
-    <row r="776" ht="15.75" customHeight="1" s="6"/>
-    <row r="777" ht="15.75" customHeight="1" s="6"/>
-    <row r="778" ht="15.75" customHeight="1" s="6"/>
-    <row r="779" ht="15.75" customHeight="1" s="6"/>
-    <row r="780" ht="15.75" customHeight="1" s="6"/>
-    <row r="781" ht="15.75" customHeight="1" s="6"/>
-    <row r="782" ht="15.75" customHeight="1" s="6"/>
-    <row r="783" ht="15.75" customHeight="1" s="6"/>
-    <row r="784" ht="15.75" customHeight="1" s="6"/>
-    <row r="785" ht="15.75" customHeight="1" s="6"/>
-    <row r="786" ht="15.75" customHeight="1" s="6"/>
-    <row r="787" ht="15.75" customHeight="1" s="6"/>
-    <row r="788" ht="15.75" customHeight="1" s="6"/>
-    <row r="789" ht="15.75" customHeight="1" s="6"/>
-    <row r="790" ht="15.75" customHeight="1" s="6"/>
-    <row r="791" ht="15.75" customHeight="1" s="6"/>
-    <row r="792" ht="15.75" customHeight="1" s="6"/>
-    <row r="793" ht="15.75" customHeight="1" s="6"/>
-    <row r="794" ht="15.75" customHeight="1" s="6"/>
-    <row r="795" ht="15.75" customHeight="1" s="6"/>
-    <row r="796" ht="15.75" customHeight="1" s="6"/>
-    <row r="797" ht="15.75" customHeight="1" s="6"/>
-    <row r="798" ht="15.75" customHeight="1" s="6"/>
-    <row r="799" ht="15.75" customHeight="1" s="6"/>
-    <row r="800" ht="15.75" customHeight="1" s="6"/>
-    <row r="801" ht="15.75" customHeight="1" s="6"/>
-    <row r="802" ht="15.75" customHeight="1" s="6"/>
-    <row r="803" ht="15.75" customHeight="1" s="6"/>
-    <row r="804" ht="15.75" customHeight="1" s="6"/>
-    <row r="805" ht="15.75" customHeight="1" s="6"/>
-    <row r="806" ht="15.75" customHeight="1" s="6"/>
-    <row r="807" ht="15.75" customHeight="1" s="6"/>
-    <row r="808" ht="15.75" customHeight="1" s="6"/>
-    <row r="809" ht="15.75" customHeight="1" s="6"/>
-    <row r="810" ht="15.75" customHeight="1" s="6"/>
-    <row r="811" ht="15.75" customHeight="1" s="6"/>
-    <row r="812" ht="15.75" customHeight="1" s="6"/>
-    <row r="813" ht="15.75" customHeight="1" s="6"/>
-    <row r="814" ht="15.75" customHeight="1" s="6"/>
-    <row r="815" ht="15.75" customHeight="1" s="6"/>
-    <row r="816" ht="15.75" customHeight="1" s="6"/>
-    <row r="817" ht="15.75" customHeight="1" s="6"/>
-    <row r="818" ht="15.75" customHeight="1" s="6"/>
-    <row r="819" ht="15.75" customHeight="1" s="6"/>
-    <row r="820" ht="15.75" customHeight="1" s="6"/>
-    <row r="821" ht="15.75" customHeight="1" s="6"/>
-    <row r="822" ht="15.75" customHeight="1" s="6"/>
-    <row r="823" ht="15.75" customHeight="1" s="6"/>
-    <row r="824" ht="15.75" customHeight="1" s="6"/>
-    <row r="825" ht="15.75" customHeight="1" s="6"/>
-    <row r="826" ht="15.75" customHeight="1" s="6"/>
-    <row r="827" ht="15.75" customHeight="1" s="6"/>
-    <row r="828" ht="15.75" customHeight="1" s="6"/>
-    <row r="829" ht="15.75" customHeight="1" s="6"/>
-    <row r="830" ht="15.75" customHeight="1" s="6"/>
-    <row r="831" ht="15.75" customHeight="1" s="6"/>
-    <row r="832" ht="15.75" customHeight="1" s="6"/>
-    <row r="833" ht="15.75" customHeight="1" s="6"/>
-    <row r="834" ht="15.75" customHeight="1" s="6"/>
-    <row r="835" ht="15.75" customHeight="1" s="6"/>
-    <row r="836" ht="15.75" customHeight="1" s="6"/>
-    <row r="837" ht="15.75" customHeight="1" s="6"/>
-    <row r="838" ht="15.75" customHeight="1" s="6"/>
-    <row r="839" ht="15.75" customHeight="1" s="6"/>
-    <row r="840" ht="15.75" customHeight="1" s="6"/>
-    <row r="841" ht="15.75" customHeight="1" s="6"/>
-    <row r="842" ht="15.75" customHeight="1" s="6"/>
-    <row r="843" ht="15.75" customHeight="1" s="6"/>
-    <row r="844" ht="15.75" customHeight="1" s="6"/>
-    <row r="845" ht="15.75" customHeight="1" s="6"/>
-    <row r="846" ht="15.75" customHeight="1" s="6"/>
-    <row r="847" ht="15.75" customHeight="1" s="6"/>
-    <row r="848" ht="15.75" customHeight="1" s="6"/>
-    <row r="849" ht="15.75" customHeight="1" s="6"/>
-    <row r="850" ht="15.75" customHeight="1" s="6"/>
-    <row r="851" ht="15.75" customHeight="1" s="6"/>
-    <row r="852" ht="15.75" customHeight="1" s="6"/>
-    <row r="853" ht="15.75" customHeight="1" s="6"/>
-    <row r="854" ht="15.75" customHeight="1" s="6"/>
-    <row r="855" ht="15.75" customHeight="1" s="6"/>
-    <row r="856" ht="15.75" customHeight="1" s="6"/>
-    <row r="857" ht="15.75" customHeight="1" s="6"/>
-    <row r="858" ht="15.75" customHeight="1" s="6"/>
-    <row r="859" ht="15.75" customHeight="1" s="6"/>
-    <row r="860" ht="15.75" customHeight="1" s="6"/>
-    <row r="861" ht="15.75" customHeight="1" s="6"/>
-    <row r="862" ht="15.75" customHeight="1" s="6"/>
-    <row r="863" ht="15.75" customHeight="1" s="6"/>
-    <row r="864" ht="15.75" customHeight="1" s="6"/>
-    <row r="865" ht="15.75" customHeight="1" s="6"/>
-    <row r="866" ht="15.75" customHeight="1" s="6"/>
-    <row r="867" ht="15.75" customHeight="1" s="6"/>
-    <row r="868" ht="15.75" customHeight="1" s="6"/>
-    <row r="869" ht="15.75" customHeight="1" s="6"/>
-    <row r="870" ht="15.75" customHeight="1" s="6"/>
-    <row r="871" ht="15.75" customHeight="1" s="6"/>
-    <row r="872" ht="15.75" customHeight="1" s="6"/>
-    <row r="873" ht="15.75" customHeight="1" s="6"/>
-    <row r="874" ht="15.75" customHeight="1" s="6"/>
-    <row r="875" ht="15.75" customHeight="1" s="6"/>
-    <row r="876" ht="15.75" customHeight="1" s="6"/>
-    <row r="877" ht="15.75" customHeight="1" s="6"/>
-    <row r="878" ht="15.75" customHeight="1" s="6"/>
-    <row r="879" ht="15.75" customHeight="1" s="6"/>
-    <row r="880" ht="15.75" customHeight="1" s="6"/>
-    <row r="881" ht="15.75" customHeight="1" s="6"/>
-    <row r="882" ht="15.75" customHeight="1" s="6"/>
-    <row r="883" ht="15.75" customHeight="1" s="6"/>
-    <row r="884" ht="15.75" customHeight="1" s="6"/>
-    <row r="885" ht="15.75" customHeight="1" s="6"/>
-    <row r="886" ht="15.75" customHeight="1" s="6"/>
-    <row r="887" ht="15.75" customHeight="1" s="6"/>
-    <row r="888" ht="15.75" customHeight="1" s="6"/>
-    <row r="889" ht="15.75" customHeight="1" s="6"/>
-    <row r="890" ht="15.75" customHeight="1" s="6"/>
-    <row r="891" ht="15.75" customHeight="1" s="6"/>
-    <row r="892" ht="15.75" customHeight="1" s="6"/>
-    <row r="893" ht="15.75" customHeight="1" s="6"/>
-    <row r="894" ht="15.75" customHeight="1" s="6"/>
-    <row r="895" ht="15.75" customHeight="1" s="6"/>
-    <row r="896" ht="15.75" customHeight="1" s="6"/>
-    <row r="897" ht="15.75" customHeight="1" s="6"/>
-    <row r="898" ht="15.75" customHeight="1" s="6"/>
-    <row r="899" ht="15.75" customHeight="1" s="6"/>
-    <row r="900" ht="15.75" customHeight="1" s="6"/>
-    <row r="901" ht="15.75" customHeight="1" s="6"/>
-    <row r="902" ht="15.75" customHeight="1" s="6"/>
-    <row r="903" ht="15.75" customHeight="1" s="6"/>
-    <row r="904" ht="15.75" customHeight="1" s="6"/>
-    <row r="905" ht="15.75" customHeight="1" s="6"/>
-    <row r="906" ht="15.75" customHeight="1" s="6"/>
-    <row r="907" ht="15.75" customHeight="1" s="6"/>
-    <row r="908" ht="15.75" customHeight="1" s="6"/>
-    <row r="909" ht="15.75" customHeight="1" s="6"/>
-    <row r="910" ht="15.75" customHeight="1" s="6"/>
-    <row r="911" ht="15.75" customHeight="1" s="6"/>
-    <row r="912" ht="15.75" customHeight="1" s="6"/>
-    <row r="913" ht="15.75" customHeight="1" s="6"/>
-    <row r="914" ht="15.75" customHeight="1" s="6"/>
-    <row r="915" ht="15.75" customHeight="1" s="6"/>
-    <row r="916" ht="15.75" customHeight="1" s="6"/>
-    <row r="917" ht="15.75" customHeight="1" s="6"/>
-    <row r="918" ht="15.75" customHeight="1" s="6"/>
-    <row r="919" ht="15.75" customHeight="1" s="6"/>
-    <row r="920" ht="15.75" customHeight="1" s="6"/>
-    <row r="921" ht="15.75" customHeight="1" s="6"/>
-    <row r="922" ht="15.75" customHeight="1" s="6"/>
-    <row r="923" ht="15.75" customHeight="1" s="6"/>
-    <row r="924" ht="15.75" customHeight="1" s="6"/>
-    <row r="925" ht="15.75" customHeight="1" s="6"/>
-    <row r="926" ht="15.75" customHeight="1" s="6"/>
-    <row r="927" ht="15.75" customHeight="1" s="6"/>
-    <row r="928" ht="15.75" customHeight="1" s="6"/>
-    <row r="929" ht="15.75" customHeight="1" s="6"/>
-    <row r="930" ht="15.75" customHeight="1" s="6"/>
-    <row r="931" ht="15.75" customHeight="1" s="6"/>
-    <row r="932" ht="15.75" customHeight="1" s="6"/>
-    <row r="933" ht="15.75" customHeight="1" s="6"/>
-    <row r="934" ht="15.75" customHeight="1" s="6"/>
-    <row r="935" ht="15.75" customHeight="1" s="6"/>
-    <row r="936" ht="15.75" customHeight="1" s="6"/>
-    <row r="937" ht="15.75" customHeight="1" s="6"/>
-    <row r="938" ht="15.75" customHeight="1" s="6"/>
-    <row r="939" ht="15.75" customHeight="1" s="6"/>
-    <row r="940" ht="15.75" customHeight="1" s="6"/>
-    <row r="941" ht="15.75" customHeight="1" s="6"/>
-    <row r="942" ht="15.75" customHeight="1" s="6"/>
-    <row r="943" ht="15.75" customHeight="1" s="6"/>
-    <row r="944" ht="15.75" customHeight="1" s="6"/>
-    <row r="945" ht="15.75" customHeight="1" s="6"/>
-    <row r="946" ht="15.75" customHeight="1" s="6"/>
-    <row r="947" ht="15.75" customHeight="1" s="6"/>
-    <row r="948" ht="15.75" customHeight="1" s="6"/>
-    <row r="949" ht="15.75" customHeight="1" s="6"/>
-    <row r="950" ht="15.75" customHeight="1" s="6"/>
-    <row r="951" ht="15.75" customHeight="1" s="6"/>
-    <row r="952" ht="15.75" customHeight="1" s="6"/>
-    <row r="953" ht="15.75" customHeight="1" s="6"/>
-    <row r="954" ht="15.75" customHeight="1" s="6"/>
-    <row r="955" ht="15.75" customHeight="1" s="6"/>
-    <row r="956" ht="15.75" customHeight="1" s="6"/>
-    <row r="957" ht="15.75" customHeight="1" s="6"/>
-    <row r="958" ht="15.75" customHeight="1" s="6"/>
-    <row r="959" ht="15.75" customHeight="1" s="6"/>
-    <row r="960" ht="15.75" customHeight="1" s="6"/>
-    <row r="961" ht="15.75" customHeight="1" s="6"/>
-    <row r="962" ht="15.75" customHeight="1" s="6"/>
-    <row r="963" ht="15.75" customHeight="1" s="6"/>
-    <row r="964" ht="15.75" customHeight="1" s="6"/>
-    <row r="965" ht="15.75" customHeight="1" s="6"/>
-    <row r="966" ht="15.75" customHeight="1" s="6"/>
-    <row r="967" ht="15.75" customHeight="1" s="6"/>
-    <row r="968" ht="15.75" customHeight="1" s="6"/>
-    <row r="969" ht="15.75" customHeight="1" s="6"/>
-    <row r="970" ht="15.75" customHeight="1" s="6"/>
-    <row r="971" ht="15.75" customHeight="1" s="6"/>
-    <row r="972" ht="15.75" customHeight="1" s="6"/>
-    <row r="973" ht="15.75" customHeight="1" s="6"/>
-    <row r="974" ht="15.75" customHeight="1" s="6"/>
-    <row r="975" ht="15.75" customHeight="1" s="6"/>
-    <row r="976" ht="15.75" customHeight="1" s="6"/>
-    <row r="977" ht="15.75" customHeight="1" s="6"/>
-    <row r="978" ht="15.75" customHeight="1" s="6"/>
-    <row r="979" ht="15.75" customHeight="1" s="6"/>
-    <row r="980" ht="15.75" customHeight="1" s="6"/>
-    <row r="981" ht="15.75" customHeight="1" s="6"/>
-    <row r="982" ht="15.75" customHeight="1" s="6"/>
-    <row r="983" ht="15.75" customHeight="1" s="6"/>
-    <row r="984" ht="15.75" customHeight="1" s="6"/>
-    <row r="985" ht="15.75" customHeight="1" s="6"/>
-    <row r="986" ht="15.75" customHeight="1" s="6"/>
-    <row r="987" ht="15.75" customHeight="1" s="6"/>
-    <row r="988" ht="15.75" customHeight="1" s="6"/>
-    <row r="989" ht="15.75" customHeight="1" s="6"/>
-    <row r="990" ht="15.75" customHeight="1" s="6"/>
-    <row r="991" ht="15.75" customHeight="1" s="6"/>
-    <row r="992" ht="15.75" customHeight="1" s="6"/>
-    <row r="993" ht="15.75" customHeight="1" s="6"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="B10:B14"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D10:D14"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C10:C14"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B21:B22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,203 +637,148 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>USERS_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no users exist</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify empty users list state</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab with no users in system.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Appropriate empty state message should display (e.g., "No users found").</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>USERS_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Verify Users List scrolling</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>User is logged in, multiple users exist</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify users list scrolling functionality</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>List should scroll smoothly; alphabetical headers should remain visible during scroll.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>USERS_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Verify user selection</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify clicking on a user opens conversation</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on any user (e.g., "John Paul").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Chat/conversation window should open with selected user.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>USERS_008</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify selected user visual feedback</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Click on a user.
-3. Observe visual indication.</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Selected user should show visual highlight (e.g., background color change).</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>USERS_009</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search functionality</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Users tab</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify search field is visible and accessible</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Observe search field at top.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -845,7 +790,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>USERS_010</t>
+          <t>USERS_008</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -853,10 +798,85 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>Verify selected user visual feedback</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Click on a user.
+3. Observe visual indication.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Selected user should show visual highlight (e.g., background color change).</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>USERS_009</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search functionality</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Users tab</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify search field is visible and accessible</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Observe search field at top.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Search field should be visible with placeholder text "Search".</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>USERS_010</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Verify search by full name</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on search field.
@@ -864,85 +884,21 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Only "John Paul" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>USERS_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify search by partial first name</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Type "Geo" in search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>"George Alan" should appear in filtered results.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>USERS_012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify search by partial last name</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Type "Grace" in search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>"Nancy Grace" should appear in filtered results.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>USERS_013</t>
+          <t>USERS_011</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -950,75 +906,63 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify case-insensitive search</t>
+          <t>Verify search by partial first name</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type "SUSAN" in search field.
+2. Type "Geo" in search field.
 3. Observe results.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>"Susan Marie" should appear regardless of case used in search.</t>
+          <t>"George Alan" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>USERS_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search functionality</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Users tab</t>
-        </is>
-      </c>
+          <t>USERS_012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify search with no matching results</t>
+          <t>Verify search by partial last name</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type "XYZ123" in search field.
+2. Type "Grace" in search field.
 3. Observe results.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display with message like "No users found" or "No results".</t>
+          <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>USERS_015</t>
+          <t>USERS_013</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -1026,86 +970,182 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Verify case-insensitive search</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Type "SUSAN" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>"Susan Marie" should appear regardless of case used in search.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>USERS_014</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search functionality</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Users tab</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with no matching results</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Type "XYZ123" in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display with message like "No users found" or "No results".</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>USERS_015</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "@#$%" in search field.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>USERS_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify search with only spaces</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type multiple spaces in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Should show all users or trim spaces and show full list.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>USERS_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type search query.
@@ -1113,204 +1153,53 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Full users list should be restored with all users visible.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>USERS_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Start typing in search field.
 3. Observe list updates.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Users list should filter in real-time as user types each character.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>USERS_019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Verify search with minimum characters</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Type single character "J".
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>USERS_020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Users module on desktop browser</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on desktop.
-2. Navigate to Users tab.
-3. Resize browser window.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Layout should adjust dynamically; list and search should remain functional.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>USERS_021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verify Users module on mobile device</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Users tab.
-3. Check layout.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Users list and search should fit screen properly without horizontal scroll.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>USERS_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Users tab highlight in navigation</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Users tab in bottom navigation.
-2. Observe tab appearance.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Users tab should be highlighted/selected (purple icon as shown).</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>USERS_023</t>
+          <t>USERS_019</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1318,102 +1207,263 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Verify search with minimum characters</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Type single character "J".
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>USERS_020</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users module on desktop browser</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Navigate to Users tab.
+3. Resize browser window.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Layout should adjust dynamically; list and search should remain functional.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>USERS_021</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users module on mobile device</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Users tab.
+3. Check layout.</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Users list and search should fit screen properly without horizontal scroll.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>USERS_022</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users tab highlight in navigation</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on Users tab in bottom navigation.
+2. Observe tab appearance.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Users tab should be highlighted/selected (purple icon as shown).</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>USERS_023</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>1. Click on Users tab.
 2. Click on Chats tab.
 3. Click back on Users tab.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Users list should reload correctly.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>USERS_024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Verify Users List loading</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Users tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while users list is being fetched.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>USERS_025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Users tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
@@ -1951,7 +2001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2139,35 +2189,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>USERS_039</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>USERS_039</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Verify user list when server returns error</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>1. Simulate server error.
 2. Open users tab.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Error message should display with retry option. No crash.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -637,72 +637,129 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>USERS_006</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users List scrolling</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, multiple users exist</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify users list scrolling functionality</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Scroll down through the list.
+3. Scroll back up.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>List should scroll smoothly; alphabetical headers should remain visible during scroll.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>USERS_005</t>
+          <t>USERS_007</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Verify Users List display</t>
+          <t>Verify user selection</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, no users exist</t>
+          <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify empty users list state</t>
+          <t>Verify clicking on a user opens conversation</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Users tab with no users in system.
-2. Observe display.</t>
+          <t>1. Navigate to Users tab.
+2. Click on any user (e.g., "John Paul").
+3. Observe result.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Appropriate empty state message should display (e.g., "No users found").</t>
+          <t>Chat/conversation window should open with selected user.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>USERS_008</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="n"/>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify selected user visual feedback</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Click on a user.
+3. Observe visual indication.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Selected user should show visual highlight (e.g., background color change).</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Low</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>USERS_006</t>
+          <t>USERS_009</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -712,73 +769,61 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Verify Users List scrolling</t>
+          <t>Verify Search functionality</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, multiple users exist</t>
+          <t>User is logged in and on Users tab</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify users list scrolling functionality</t>
+          <t>Verify search field is visible and accessible</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Scroll down through the list.
-3. Scroll back up.</t>
+2. Observe search field at top.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>List should scroll smoothly; alphabetical headers should remain visible during scroll.</t>
+          <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>USERS_007</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Verify user selection</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and navigated to Users tab</t>
-        </is>
-      </c>
+          <t>USERS_010</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify clicking on a user opens conversation</t>
+          <t>Verify search by full name</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Click on any user (e.g., "John Paul").
-3. Observe result.</t>
+2. Click on search field.
+3. Type "John Paul".
+4. Observe results.</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Chat/conversation window should open with selected user.</t>
+          <t>Only "John Paul" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -790,7 +835,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>USERS_008</t>
+          <t>USERS_011</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -798,74 +843,63 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Verify selected user visual feedback</t>
+          <t>Verify search by partial first name</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Click on a user.
-3. Observe visual indication.</t>
+2. Type "Geo" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Selected user should show visual highlight (e.g., background color change).</t>
+          <t>"George Alan" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Medium / Low</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>USERS_009</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search functionality</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Users tab</t>
-        </is>
-      </c>
+          <t>USERS_012</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify search field is visible and accessible</t>
+          <t>Verify search by partial last name</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Observe search field at top.</t>
+2. Type "Grace" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Search field should be visible with placeholder text "Search".</t>
+          <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>USERS_010</t>
+          <t>USERS_013</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -873,64 +907,76 @@
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify search by full name</t>
+          <t>Verify case-insensitive search</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Click on search field.
-3. Type "John Paul".
-4. Observe results.</t>
+2. Type "SUSAN" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Only "John Paul" should appear in filtered results.</t>
+          <t>"Susan Marie" should appear regardless of case used in search.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>USERS_011</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
+          <t>USERS_017</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search functionality</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Users tab</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Verify search by partial first name</t>
+          <t>Verify clearing search field</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type "Geo" in search field.
-3. Observe results.</t>
+2. Type search query.
+3. Clear the search field.
+4. Observe results.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>"George Alan" should appear in filtered results.</t>
+          <t>Full users list should be restored with all users visible.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>USERS_012</t>
+          <t>USERS_018</t>
         </is>
       </c>
       <c r="B15" s="2" t="n"/>
@@ -938,31 +984,31 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify search by partial last name</t>
+          <t>Verify real-time search filtering</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type "Grace" in search field.
-3. Observe results.</t>
+2. Start typing in search field.
+3. Observe list updates.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>"Nancy Grace" should appear in filtered results.</t>
+          <t>Users list should filter in real-time as user types each character.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>USERS_013</t>
+          <t>USERS_019</t>
         </is>
       </c>
       <c r="B16" s="2" t="n"/>
@@ -970,19 +1016,19 @@
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify case-insensitive search</t>
+          <t>Verify search with minimum characters</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type "SUSAN" in search field.
+2. Type single character "J".
 3. Observe results.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>"Susan Marie" should appear regardless of case used in search.</t>
+          <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -992,95 +1038,128 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>USERS_020</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users module on desktop browser</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Open application on desktop.
+2. Navigate to Users tab.
+3. Resize browser window.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Layout should adjust dynamically; list and search should remain functional.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>USERS_014</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Verify Search functionality</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Users tab</t>
-        </is>
-      </c>
+          <t>USERS_021</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify search with no matching results</t>
+          <t>Verify Users module on mobile device</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Users tab.
-2. Type "XYZ123" in search field.
-3. Observe results.</t>
+          <t>1. Open application on mobile browser/device.
+2. Navigate to Users tab.
+3. Check layout.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display with message like "No users found" or "No results".</t>
+          <t>Users list and search should fit screen properly without horizontal scroll.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>USERS_015</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
+          <t>USERS_022</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Verify navigation</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Verify search with special characters</t>
+          <t>Verify Users tab highlight in navigation</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Users tab.
-2. Type "@#$%" in search field.
-3. Observe behavior.</t>
+          <t>1. Click on Users tab in bottom navigation.
+2. Observe tab appearance.</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Application should handle gracefully; show no results or ignore special characters.</t>
+          <t>Users tab should be highlighted/selected (purple icon as shown).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Low / Medium</t>
+          <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>USERS_016</t>
+          <t>USERS_023</t>
         </is>
       </c>
       <c r="B20" s="2" t="n"/>
@@ -1088,24 +1167,24 @@
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify search with only spaces</t>
+          <t>Verify navigation between tabs</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Users tab.
-2. Type multiple spaces in search field.
-3. Observe results.</t>
+          <t>1. Click on Users tab.
+2. Click on Chats tab.
+3. Click back on Users tab.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Should show all users or trim spaces and show full list.</t>
+          <t>Navigation should work smoothly; Users list should reload correctly.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
@@ -1122,72 +1201,82 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>USERS_017</t>
+          <t>USERS_005</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Verify Search functionality</t>
+          <t>Verify Users List display</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Users tab</t>
+          <t>User is logged in, no users exist</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Verify clearing search field</t>
+          <t>Verify empty users list state</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Navigate to Users tab.
-2. Type search query.
-3. Clear the search field.
-4. Observe results.</t>
+          <t>1. Navigate to Users tab with no users in system.
+2. Observe display.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Full users list should be restored with all users visible.</t>
+          <t>Appropriate empty state message should display (e.g., "No users found").</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>USERS_018</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
+          <t>USERS_014</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search functionality</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and on Users tab</t>
+        </is>
+      </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify real-time search filtering</t>
+          <t>Verify search with no matching results</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Start typing in search field.
-3. Observe list updates.</t>
+2. Type "XYZ123" in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Users list should filter in real-time as user types each character.</t>
+          <t>Empty state should display with message like "No users found" or "No results".</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1199,7 +1288,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>USERS_019</t>
+          <t>USERS_015</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -1207,263 +1296,134 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Verify search with minimum characters</t>
+          <t>Verify search with special characters</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
-2. Type single character "J".
-3. Observe results.</t>
+2. Type "@#$%" in search field.
+3. Observe behavior.</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
+          <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>USERS_020</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>USERS_016</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify Users module on desktop browser</t>
+          <t>Verify search with only spaces</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Open application on desktop.
-2. Navigate to Users tab.
-3. Resize browser window.</t>
+          <t>1. Navigate to Users tab.
+2. Type multiple spaces in search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Layout should adjust dynamically; list and search should remain functional.</t>
+          <t>Should show all users or trim spaces and show full list.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>USERS_021</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
+          <t>USERS_024</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Verify Users List loading</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, slow network</t>
+        </is>
+      </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify Users module on mobile device</t>
+          <t>Verify loading state during slow connection</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1. Open application on mobile browser/device.
-2. Navigate to Users tab.
-3. Check layout.</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Users list and search should fit screen properly without horizontal scroll.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>USERS_022</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify Users tab highlight in navigation</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Users tab in bottom navigation.
-2. Observe tab appearance.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Users tab should be highlighted/selected (purple icon as shown).</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>USERS_023</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Verify navigation between tabs</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on Users tab.
-2. Click on Chats tab.
-3. Click back on Users tab.</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Navigation should work smoothly; Users list should reload correctly.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>USERS_024</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Verify Users List loading</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, slow network</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Verify loading state during slow connection</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Users tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while users list is being fetched.</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>USERS_025</t>
         </is>
       </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Users tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,377 +465,377 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify users list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Users" tab in bottom navigation.
 3. Observe users list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Users list should display with user names, profile pictures, and alphabetical section headers (G, I, J, N, S).</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify alphabetical grouping of users</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe section headers.
 3. Verify user placement under headers.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Users should be grouped alphabetically by first name with correct letter headers displayed.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>USERS_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify user profile picture display</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe profile pictures next to each user.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Profile pictures should display correctly; default avatar shown for users without pictures.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>USERS_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify user name display format</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe user names in the list.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>User names should display in "First Name Last Name" format clearly and legibly.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>USERS_006</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Verify Users List scrolling</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>User is logged in, multiple users exist</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify users list scrolling functionality</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>List should scroll smoothly; alphabetical headers should remain visible during scroll.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>USERS_007</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Verify user selection</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify clicking on a user opens conversation</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on any user (e.g., "John Paul").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Chat/conversation window should open with selected user.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>USERS_008</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify selected user visual feedback</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on a user.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Selected user should show visual highlight (e.g., background color change).</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>USERS_009</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify search field is visible and accessible</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe search field at top.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>USERS_010</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify search by full name</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on search field.
@@ -821,140 +843,140 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Only "John Paul" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>USERS_011</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify search by partial first name</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "Geo" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>"George Alan" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>USERS_012</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify search by partial last name</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "Grace" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>USERS_013</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "SUSAN" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>"Susan Marie" should appear regardless of case used in search.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>USERS_017</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type search query.
@@ -962,470 +984,1014 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Full users list should be restored with all users visible.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>USERS_018</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Start typing in search field.
 3. Observe list updates.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Users list should filter in real-time as user types each character.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>USERS_019</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify search with minimum characters</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type single character "J".
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>USERS_020</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify Users module on desktop browser</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Users tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; list and search should remain functional.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>USERS_021</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify Users module on mobile device</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Users tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Users list and search should fit screen properly without horizontal scroll.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>USERS_022</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify Users tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Click on Users tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Users tab should be highlighted/selected (purple icon as shown).</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>USERS_023</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Click on Users tab.
 2. Click on Chats tab.
 3. Click back on Users tab.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Users list should reload correctly.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="n"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>USERS_015</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Verify search with special characters</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Type "@#$%" in search field.
+3. Observe behavior.</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Application should handle gracefully; show no results or ignore special characters.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>USERS_016</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Verify search with only spaces</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>1. Navigate to Users tab.
+2. Type multiple spaces in search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Should show all users or trim spaces and show full list.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>USERS_025</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in, network error</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Verify error handling on network failure</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network.
+2. Navigate to Users tab.
+3. Observe error handling.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate error message should display with retry option.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>USR_001</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Block User</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>User details open</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Verify block user option available</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>1. Open user details
+2. Check for block option</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Block user option visible</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>USR_002</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Block User Action</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Block option clicked</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Verify user blocked successfully</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>1. Click block user
+2. Confirm</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>User blocked, chat composer disabled</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>USR_003</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Unblock User</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>User is blocked</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Verify unblock option available for blocked user</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>1. Open blocked user details
+2. Check for unblock</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Unblock option visible</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>USR_004</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Unblock User Action</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Unblock clicked</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Verify user unblocked successfully</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>1. Click unblock
+2. Confirm</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>User unblocked, chat composer re-enabled</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>USR_005</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>View Profile</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>User details open</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Verify view profile option available</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>1. Open user details
+2. Check for view profile</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>View profile option visible</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>USR_006</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>View Profile Action</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>View profile clicked</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Verify profile information displayed</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. Click view profile</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>User profile details shown (name, avatar, status)</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>USR_007</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Section Headers</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Users list with multiple users</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Verify alphabetical section headers</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. Open users list
+2. Check for section headers</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Alphabetical section headers (A, B, C...) visible</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>USR_008</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Section Headers Scroll</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Long users list</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Verify section headers while scrolling</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll through users list</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Section headers visible for each letter group</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>USR_009</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Online Status Indicator</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>hideUserStatus=false</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Verify online/offline status shown</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. Check user list items</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Green dot for online, grey for offline</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>USERS_005</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>User is logged in, no users exist</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Verify empty users list state</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab with no users in system.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>Appropriate empty state message should display (e.g., "No users found").</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>USERS_014</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Verify search with no matching results</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "XYZ123" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>Empty state should display with message like "No users found" or "No results".</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>USERS_015</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Verify search with special characters</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Type "@#$%" in search field.
-3. Observe behavior.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Application should handle gracefully; show no results or ignore special characters.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>USERS_016</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify search with only spaces</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to Users tab.
-2. Type multiple spaces in search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Should show all users or trim spaces and show full list.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>USERS_024</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Verify Users List loading</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Users tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>Loading indicator should display while users list is being fetched.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>USERS_025</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network error</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify error handling on network failure</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Navigate to Users tab.
-3. Observe error handling.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Appropriate error message should display with retry option.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>USR_010</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Block - Already Blocked</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>User already blocked</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Verify block option changes to unblock</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1. Check blocked user options</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Only unblock option shown, not block</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>USR_011</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>View Profile - No Profile</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>User has minimal profile</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling of empty profile data</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1. View profile of user with no details</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate fallback/empty state shown</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>USR_012</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>User Status Hidden</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>hideUserStatus=true</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Verify status indicator hidden</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1. Set hideUserStatus=true
+2. Check users</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>No online/offline indicators visible</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>USR_013</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Block Self</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Own profile</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Verify cannot block self</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>1. Check own profile options</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Block option not available for self</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1437,139 +2003,312 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: User Module with Chat</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify clicking user opens one-on-one chat</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Click on a user in the list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>One-on-one chat should open with that user. Message history should load.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_027</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Integration: User Module with Conversation List</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify starting chat from users list creates conversation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Click on a user with no prior conversation.
 2. Send a message.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>New conversation should appear in conversation list after sending first message.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>USR_014</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Block + Conversation List</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversation list updates after block</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Check conversation list</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Blocked user conversation shows blocked state</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>USR_015</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Block + Message Composer</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify composer disabled after blocking</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Open chat</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Composer disabled with blocked message</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>USR_016</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unblock + Resume Chat</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>User unblocked</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify chat resumes after unblock</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Unblock user
+2. Open chat</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Composer enabled, can send messages again</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>USR_017</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Block + Incoming Messages</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify blocked user messages not received</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Blocked user sends message</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Message not received or shown</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1581,198 +2320,329 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_028</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: User Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify user list updates when new user registers</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. A new user registers on the platform.
 2. Refresh user list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>New user should appear in the user list.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_029</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify user list after blocking a user</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Blocked user should be handled per policy (hidden, marked, or unchanged in list).</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>USERS_030</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify user list after unblocking a user</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Unblock a previously blocked user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>User should be accessible again in the list.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>USERS_031</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify user online status updates in real-time</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Observe a user in the list.
 2. That user goes online/offline.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Online status indicator should update in real-time.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>USR_018</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Block After Reconnect</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Network reconnected</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify block status persists after reconnect</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Disconnect
+3. Reconnect</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>User still blocked after reconnection</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>USR_019</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Section Headers After Search</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Search performed then cleared</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify section headers restore after search clear</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Search users
+2. Clear search</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Section headers visible again</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>USR_020</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Unblock After App Restart</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>User unblocked then app restarted</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verify unblock persists after restart</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>1. Unblock user
+2. Restart app</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>User still unblocked</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1784,168 +2654,253 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>USERS_033</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Verify user list does not expose sensitive user data</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. Observe user list entries.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Only public info (name, avatar, status) should display. No email, phone, or private data.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>USERS_034</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in user search</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '&lt;script&gt;alert(1)&lt;/script&gt;' in user search.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Input should be sanitized. No script execution.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>USR_021</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Block Auth Verification</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Valid session</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify block requires authentication</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt block without auth</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Block fails without valid authentication</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>USERS_032</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Security: User Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>User is not logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify user list not accessible without authentication</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Try to access user list without logging in.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Should redirect to login. No user data exposed.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>USERS_033</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verify user list does not expose sensitive user data</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Observe user list entries.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Only public info (name, avatar, status) should display. No email, phone, or private data.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>USERS_034</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify XSS prevention in user search</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Type '&lt;script&gt;alert(1)&lt;/script&gt;' in user search.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Input should be sanitized. No script execution.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>USR_022</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Block Bypass via API</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Direct API call</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify block cannot be bypassed</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to message blocked user via API</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Message rejected for blocked user</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1961,235 +2916,353 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_035</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: User Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify user list with 10000+ users</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Open users tab on a platform with 10000+ users.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Users should load with pagination/infinite scroll. Alphabetical grouping should work.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_036</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify user with very long name</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe a user with a 100+ character name in the list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Name should truncate with ellipsis. No layout breaking.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>USERS_037</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify user with special characters in name</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Observe a user with emojis, unicode, or special chars in name.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Name should display correctly.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>USERS_038</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify user search with partial name</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Search for first 2 characters of a user's name.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>All users matching the partial name should appear.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n"/>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>USR_023</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Block/Unblock Rapid Toggle</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Rapid block/unblock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify rapid toggle handled correctly</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Block then immediately unblock
+2. Check status</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Final state correctly reflected</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>USR_024</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Section Headers - All Same Letter</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>All users start with 'A'</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify single section header</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Load users all starting with 'A'</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Single 'A' section header shown</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>USERS_039</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify user list when server returns error</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Simulate server error.
 2. Open users tab.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Error message should display with retry option. No crash.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>USR_025</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Block Offline User</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Target user is offline</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify can block offline user</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Block an offline user</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>User blocked regardless of online status</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2205,160 +3278,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_040</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: User Module</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify user list with exactly 0 users (only self)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Login on a platform with no other users.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Empty state should display or only self should appear.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_041</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify user list with exactly 1 other user</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Login on a platform with 1 other user.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Single user should display correctly with all elements.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>USERS_042</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify search with exactly 1 character</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Type a single character in user search.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Should filter users or show minimum character requirement.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>USR_026</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Users List Limit 30</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Default limit</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify 30 users loaded initially</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Open users list</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>30 users loaded, more on scroll</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>USR_027</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Empty Users List</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>No users available</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty state with 0 users</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. No users in app</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Empty state displayed</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2374,160 +3532,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>USERS_043</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: User Status</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify online user display</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Observe an online user in the list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should show green online indicator and be at top of list (if sorted by status).</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>USERS_044</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify offline user display</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe an offline user in the list.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Should show grey/no indicator. Last seen time may display.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>USERS_045</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify away/busy user display (if supported)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Observe a user with away/busy status.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Should show appropriate status indicator (yellow/red dot).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>USR_028</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Online User</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>User is online</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify online user display</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Check online user in list</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Green status indicator, name, avatar shown</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>USR_029</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Offline User</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>User is offline</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify offline user display</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Check offline user in list</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Grey/no status indicator, name, avatar shown</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>USR_030</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Blocked User</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User is blocked</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify blocked user display</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Check blocked user in list</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Blocked indicator or different styling shown</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>

--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -81,11 +81,12 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +100,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,7 +473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -521,321 +529,321 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>USERS_001</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify users list loads correctly</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Login to application.
 2. Click on "Users" tab in bottom navigation.
 3. Observe users list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Users list should display with user names, profile pictures, and alphabetical section headers (G, I, J, N, S).</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>USERS_002</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify alphabetical grouping of users</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe section headers.
 3. Verify user placement under headers.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Users should be grouped alphabetically by first name with correct letter headers displayed.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>USERS_003</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify user profile picture display</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe profile pictures next to each user.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Profile pictures should display correctly; default avatar shown for users without pictures.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>USERS_004</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify user name display format</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe user names in the list.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>User names should display in "First Name Last Name" format clearly and legibly.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>USERS_006</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Verify Users List scrolling</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>User is logged in, multiple users exist</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify users list scrolling functionality</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Scroll down through the list.
 3. Scroll back up.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>List should scroll smoothly; alphabetical headers should remain visible during scroll.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>USERS_007</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Verify user selection</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>User is logged in and navigated to Users tab</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify clicking on a user opens conversation</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on any user (e.g., "John Paul").
 3. Observe result.</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Chat/conversation window should open with selected user.</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>USERS_008</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Verify selected user visual feedback</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on a user.
 3. Observe visual indication.</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Selected user should show visual highlight (e.g., background color change).</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>USERS_009</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Verify search field is visible and accessible</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Observe search field at top.</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Search field should be visible with placeholder text "Search".</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>USERS_010</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify search by full name</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Click on search field.
@@ -843,140 +851,140 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Only "John Paul" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>USERS_011</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Verify search by partial first name</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "Geo" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>"George Alan" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>USERS_012</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Verify search by partial last name</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "Grace" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>"Nancy Grace" should appear in filtered results.</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>USERS_013</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Verify case-insensitive search</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "SUSAN" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>"Susan Marie" should appear regardless of case used in search.</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>USERS_017</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Verify clearing search field</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type search query.
@@ -984,1012 +992,2538 @@
 4. Observe results.</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Full users list should be restored with all users visible.</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>USERS_018</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Verify real-time search filtering</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Start typing in search field.
 3. Observe list updates.</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>Users list should filter in real-time as user types each character.</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>USERS_019</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Verify search with minimum characters</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type single character "J".
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Should filter and show users starting with "J" (e.g., John Paul).</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>USERS_020</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Verify Users module on desktop browser</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Navigate to Users tab.
 3. Resize browser window.</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Layout should adjust dynamically; list and search should remain functional.</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>USERS_021</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Verify Users module on mobile device</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>1. Open application on mobile browser/device.
 2. Navigate to Users tab.
 3. Check layout.</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Users list and search should fit screen properly without horizontal scroll.</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>USERS_022</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Verify navigation</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Verify Users tab highlight in navigation</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>1. Click on Users tab in bottom navigation.
 2. Observe tab appearance.</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Users tab should be highlighted/selected (purple icon as shown).</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Medium / Low</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>USERS_023</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Verify navigation between tabs</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>1. Click on Users tab.
 2. Click on Chats tab.
 3. Click back on Users tab.</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>Navigation should work smoothly; Users list should reload correctly.</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>USERS_015</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "@#$%" in search field.
 3. Observe behavior.</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>Application should handle gracefully; show no results or ignore special characters.</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>USERS_016</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Verify search with only spaces</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type multiple spaces in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>Should show all users or trim spaces and show full list.</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>USERS_025</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>User is logged in, network error</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Verify error handling on network failure</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Navigate to Users tab.
 3. Observe error handling.</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>Appropriate error message should display with retry option.</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>USR_001</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Block User</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>User details open</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Verify block user option available</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>1. Open user details
 2. Check for block option</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>Block user option visible</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>USR_002</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Block User Action</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Block option clicked</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Verify user blocked successfully</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>1. Click block user
 2. Confirm</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>User blocked, chat composer disabled</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>USR_003</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Unblock User</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>User is blocked</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Verify unblock option available for blocked user</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>1. Open blocked user details
 2. Check for unblock</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="5" t="inlineStr">
         <is>
           <t>Unblock option visible</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>USR_004</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Unblock User Action</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Unblock clicked</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Verify user unblocked successfully</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>1. Click unblock
 2. Confirm</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>User unblocked, chat composer re-enabled</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>USR_005</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>View Profile</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>User details open</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Verify view profile option available</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>1. Open user details
 2. Check for view profile</t>
         </is>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>View profile option visible</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>USR_006</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>View Profile Action</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>View profile clicked</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Verify profile information displayed</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>1. Click view profile</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>User profile details shown (name, avatar, status)</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>USR_007</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Section Headers</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Users list with multiple users</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>Verify alphabetical section headers</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>1. Open users list
 2. Check for section headers</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>Alphabetical section headers (A, B, C...) visible</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>USR_008</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Section Headers Scroll</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Long users list</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Verify section headers while scrolling</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>1. Scroll through users list</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>Section headers visible for each letter group</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>USR_009</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Online Status Indicator</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>hideUserStatus=false</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>Verify online/offline status shown</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>1. Check user list items</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>Green dot for online, grey for offline</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>USR_031</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Region Selection</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>App launched, credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify US region is selected by default</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Open app
+2. Navigate to credentials screen
+3. Observe region selector</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>US region should be pre-selected by default</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>USR_032</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Select EU Region</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Verify user can select EU region</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>1. Click on EU region option
+2. Observe selection state</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>EU region should be highlighted as selected, US deselected</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>USR_033</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Select IN Region</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Verify user can select IN region</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>1. Click on IN region option
+2. Observe selection state</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>IN region should be highlighted as selected</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>USR_034</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Enter Valid App ID</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Verify user can enter App ID</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>1. Click App ID input field
+2. Type valid App ID
+3. Observe input</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>App ID should be accepted and displayed in the field</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>USR_035</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Enter Valid Auth Key</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Verify user can enter Auth Key</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>1. Click Auth Key input field
+2. Type valid Auth Key
+3. Observe input</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Auth Key should be accepted and displayed in the field</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>USR_036</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Submit Valid Credentials</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>All fields filled with valid data</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Verify successful submission navigates to login</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter valid App ID
+2. Enter valid Auth Key
+3. Select region
+4. Click Continue</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>CometChat SDK should initialize and navigate to /login page</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>USR_037</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - LocalStorage Persistence</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Valid credentials entered</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Verify credentials are saved to localStorage</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter App ID, Auth Key, select region
+2. Click Continue
+3. Check localStorage</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>region, appId, authKey should be stored in localStorage</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>USR_038</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Dark Mode Logo</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Dark mode enabled on device</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Verify dark mode logo is displayed</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>1. Enable dark mode in OS settings
+2. Open credentials screen
+3. Observe logo</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Dark mode CometChat logo should be displayed</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>USR_039</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Light Mode Logo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Light mode enabled on device</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify light mode logo is displayed</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Enable light mode in OS settings
+2. Open credentials screen
+3. Observe logo</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Light mode CometChat logo should be displayed</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>USR_040</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Login - Sample Users Display</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Login screen loaded, API accessible</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Verify sample users are fetched and displayed</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Navigate to login screen
+2. Wait for users to load
+3. Observe user list</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Sample users should be fetched from API and displayed with avatar, name, and UID</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>USR_041</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Login - Sample User Click Login</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Sample users displayed</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify clicking a sample user logs in</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a sample user card
+2. Wait for login
+3. Observe navigation</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>User should be logged in via CometChatUIKit.login() and navigated to /home</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>USR_042</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Login - Selection Indicator</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sample users displayed</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify selected user shows selection indicator</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Click on a sample user
+2. Observe visual feedback</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Selected user should show a checked selection indicator circle</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>USR_043</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Login - Custom UID Login</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify login with custom UID</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter a valid UID in the custom UID input
+2. Click Login button
+3. Wait for login</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>User should be logged in with the custom UID and navigated to /home</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>USR_044</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Login - Change App Credentials Link</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify Change App Credentials navigates to credentials screen</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Click 'App Credentials' link text
+2. Observe navigation</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Should clear localStorage credentials and navigate to /credentials</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>USR_045</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Login - Auto-redirect If Logged In</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>User already logged in</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify auto-redirect to home if already logged in</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Login successfully
+2. Navigate back to /login
+3. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Should automatically redirect to /home with replace:true</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>USR_046</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Login - Fallback Sample Users</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>API endpoint unreachable</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify fallback sample users are used when API fails</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Block network to sample data API
+2. Navigate to login screen
+3. Observe user list</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Fallback sample users from local sampledata.ts should be displayed</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>USR_047</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Login - Dark Mode Logo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Dark mode enabled</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify dark mode logo on login screen</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Enable dark mode
+2. Open login screen</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Dark mode CometChat logo should be displayed</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>USR_048</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Open Panel</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>User conversation selected</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify user details panel opens on header click</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Select a user conversation
+2. Click on message header
+3. Observe side panel</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>User details side panel should open showing avatar, name, status</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>USR_049</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block User Flow</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify block user with confirmation dialog</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Block option
+2. Observe confirmation dialog
+3. Click Block in dialog</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog appears, user blocked on confirm, toast shows 'Blocked successfully'</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>USR_050</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Unblock User</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>User is blocked, details panel open</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify unblock user action</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Unblock option in details
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>User should be unblocked immediately (no confirmation), action text changes to Block</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>USR_051</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block Hides Status</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify blocking hides user status</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user
+2. Observe status indicator</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>User status (online/offline) should be hidden after blocking</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>USR_052</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Unblock Shows Status</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Blocked user details panel open</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify unblocking restores status visibility</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Unblock a user
+2. Observe status indicator</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>User status should become visible again after unblocking</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>USR_053</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Delete Chat</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open, conversation exists</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify delete chat with confirmation</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Delete Chat
+2. Observe confirmation dialog
+3. Confirm deletion</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Confirmation dialog appears, conversation deleted, side panel closes, toast shown</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>USR_054</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Close Panel</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify closing the details panel</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Click close icon on panel
+2. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Side panel should close, messages view remains</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>USR_055</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block Confirmation Cancel</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Block confirmation dialog shown</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Verify canceling block confirmation</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Block
+2. In confirmation dialog click Cancel</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Dialog should close, user remains unblocked</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>USR_056</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Delete Chat Confirmation Cancel</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Delete confirmation dialog shown</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Verify canceling delete confirmation</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Delete Chat
+2. In confirmation dialog click Cancel</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Dialog should close, conversation remains</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>USERS_005</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no users exist</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Verify empty users list state</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab with no users in system.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Appropriate empty state message should display (e.g., "No users found").</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>USERS_014</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Verify search with no matching results</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "XYZ123" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with message like "No users found" or "No results".</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>USERS_024</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Verify Users List loading</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Users tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while users list is being fetched.</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>USR_010</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>Block - Already Blocked</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>User already blocked</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Verify block option changes to unblock</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Check blocked user options</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Only unblock option shown, not block</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>USR_011</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>View Profile - No Profile</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>User has minimal profile</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Verify handling of empty profile data</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. View profile of user with no details</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Appropriate fallback/empty state shown</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>USR_012</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>User Status Hidden</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>hideUserStatus=true</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Verify status indicator hidden</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Set hideUserStatus=true
 2. Check users</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>No online/offline indicators visible</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>USR_013</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Block Self</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Own profile</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Verify cannot block self</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Check own profile options</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Block option not available for self</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>USR_057</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Empty App ID</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Verify form validation for empty App ID</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave App ID empty
+2. Enter Auth Key
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit, HTML5 required validation should trigger</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>USR_058</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Empty Auth Key</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Verify form validation for empty Auth Key</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter App ID
+2. Leave Auth Key empty
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit, HTML5 required validation should trigger</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>USR_059</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Invalid App ID</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling for invalid App ID</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter invalid/random App ID
+2. Enter valid Auth Key
+3. Click Continue</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>SDK initialization should fail, appropriate error handling</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>USR_060</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Both Fields Empty</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Verify form won't submit with all fields empty</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave all fields empty
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit due to required field validation</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>USR_061</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Login - Empty Custom UID</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty UID validation</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave UID field empty
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Form should not submit due to required field validation</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>USR_062</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Login - Invalid Custom UID</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Verify login with non-existent UID</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter non-existent UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Login should fail, error logged to console</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>USR_063</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Login - No Credentials Redirect</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>No credentials in localStorage or AppConstants</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Verify redirect to credentials when no credentials exist</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear all localStorage
+2. Set empty AppConstants
+3. Navigate to /login</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Should redirect to /credentials screen</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>USR_064</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Delete Fresh Chat</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Fresh chat with no messages</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Verify delete chat disabled for fresh chats</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1. Start new chat (no messages sent)
+2. Open details
+3. Observe Delete Chat</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Delete Chat option should be visually disabled (action-item-disabled class)</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>USR_065</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Delete Chat API Failure</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Verify error handling on delete chat failure</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Delete Chat
+2. Confirm
+3. Simulate API failure</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Error should be caught and logged, app should not crash</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2007,7 +3541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2063,250 +3597,638 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>USERS_026</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Integration: User Module with Chat</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify clicking user opens one-on-one chat</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Click on a user in the list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>One-on-one chat should open with that user. Message history should load.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>USERS_027</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Integration: User Module with Conversation List</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify starting chat from users list creates conversation</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Click on a user with no prior conversation.
 2. Send a message.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>New conversation should appear in conversation list after sending first message.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>USR_014</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Block + Conversation List</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>User blocked</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify conversation list updates after block</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Block user
 2. Check conversation list</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Blocked user conversation shows blocked state</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>USR_015</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Block + Message Composer</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>User blocked</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify composer disabled after blocking</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Block user
 2. Open chat</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Composer disabled with blocked message</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>USR_016</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Unblock + Resume Chat</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>User unblocked</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify chat resumes after unblock</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Unblock user
 2. Open chat</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Composer enabled, can send messages again</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>USR_066</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - SDK Init Integration</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Valid credentials available</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify CometChat SDK initializes with provided credentials</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter valid App ID, Auth Key, region
+2. Click Continue
+3. Monitor SDK init</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>UIKitSettingsBuilder should build with correct params, SDK init succeeds</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>USR_067</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Credentials - Navigation to Login</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>SDK initialized successfully</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify navigation from credentials to login screen</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Submit valid credentials
+2. Observe navigation</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>App should navigate to /login route with replace:true</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>USR_068</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Login - CometChatUIKit.login Integration</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Valid UID available</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify CometChatUIKit.login() is called correctly</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Click sample user or enter custom UID
+2. Monitor SDK login call</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>CometChatUIKit.login(uid) should be called and return loggedInUser</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>USR_069</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Login - Sample Users API Integration</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Network available</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify sample users fetched from correct API endpoint</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Open login screen
+2. Monitor network requests</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>GET request to https://assets.cc-cluster-2.io/sampleapp/v2/sampledata.json should be made</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>USR_070</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block Event Propagation</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>User blocked from details</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify block event updates message composer</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Block user from details panel
+2. Observe message composer</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Composer should be replaced with 'Cannot send to blocked user' message with unblock link</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>USR_071</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Unblock Event Propagation</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User unblocked from details</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify unblock event restores composer</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Unblock user from details
+2. Observe message composer</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Message composer should reappear, blocked message removed</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>USR_072</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Delete Conversation Event</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Chat deleted from details</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify conversation deleted event fires</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete chat from details
+2. Monitor events</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ccConversationDeleted event should fire, conversation removed from list</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>USR_073</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block Toast Notification</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User blocked</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify toast notification on block</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Block a user
+2. Observe toast</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Toast should show 'Blocked successfully' message</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>USR_017</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Block + Incoming Messages</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>User blocked</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify blocked user messages not received</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Block user
 2. Blocked user sends message</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Message not received or shown</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>USR_074</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - SDK Init Failure</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Invalid credentials entered</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify app handles SDK initialization failure</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter invalid credentials
+2. Click Continue
+3. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>App should handle error gracefully without crashing</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2324,7 +4246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2380,267 +4302,400 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>USERS_028</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Regression: User Module</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify user list updates when new user registers</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. A new user registers on the platform.
 2. Refresh user list.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>New user should appear in the user list.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>USERS_029</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify user list after blocking a user</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Block a user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Blocked user should be handled per policy (hidden, marked, or unchanged in list).</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>USERS_030</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify user list after unblocking a user</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Unblock a previously blocked user.
 2. Observe user list.</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>User should be accessible again in the list.</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>USERS_031</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Verify user online status updates in real-time</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>1. Observe a user in the list.
 2. That user goes online/offline.</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Online status indicator should update in real-time.</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>USR_018</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Block After Reconnect</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Network reconnected</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Verify block status persists after reconnect</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>1. Block user
 2. Disconnect
 3. Reconnect</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>User still blocked after reconnection</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>USR_019</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Section Headers After Search</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Search performed then cleared</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify section headers restore after search clear</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Search users
 2. Clear search</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Section headers visible again</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>USR_075</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Re-enter After Change</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Previously logged in, credentials changed</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify credentials screen works after clearing credentials</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Login successfully
+2. Change credentials from login screen
+3. Re-enter new credentials
+4. Submit</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>New credentials should be accepted and SDK re-initialized</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>USR_076</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Login - Re-login After Logout</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>User previously logged out</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify login works after logout</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Logout from app
+2. Return to login screen
+3. Login again</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Login should work normally after logout</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>USR_077</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>User Details - Block/Unblock Toggle</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Block/Unblock text toggles correctly</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Observe action text changes to Unblock
+3. Unblock
+4. Observe text changes to Block</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Action text should toggle between Block and Unblock correctly</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>USR_020</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Unblock After App Restart</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>User unblocked then app restarted</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verify unblock persists after restart</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>1. Unblock user
 2. Restart app</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>User still unblocked</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2658,7 +4713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2714,193 +4769,417 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>USERS_033</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Verify user list does not expose sensitive user data</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>1. Observe user list entries.</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Only public info (name, avatar, status) should display. No email, phone, or private data.</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>USERS_034</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Verify XSS prevention in user search</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>1. Type '&lt;script&gt;alert(1)&lt;/script&gt;' in user search.</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Input should be sanitized. No script execution.</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>USR_021</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Block Auth Verification</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Valid session</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify block requires authentication</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>1. Attempt block without auth</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Block fails without valid authentication</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>USR_078</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Auth Key Not Masked</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verify Auth Key input is plain text type</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter Auth Key
+2. Observe input type</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Auth Key field uses type='text' (visible for dev convenience)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>USERS_032</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Security: User Module</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>User is not logged in</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Verify user list not accessible without authentication</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>1. Try to access user list without logging in.</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Should redirect to login. No user data exposed.</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>USR_022</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Block Bypass via API</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Direct API call</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify block cannot be bypassed</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>1. Try to message blocked user via API</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Message rejected for blocked user</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>USR_079</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - XSS in App ID</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS injection in App ID is handled</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as App ID
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Script should not execute, input treated as plain text</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>USR_080</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - XSS in Auth Key</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS injection in Auth Key is handled</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as Auth Key
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Script should not execute, input treated as plain text</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>USR_081</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Login - XSS in Custom UID</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS injection in UID field</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Script should not execute, treated as plain text UID</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>USR_082</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Login - SQL Injection in UID</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify SQL injection in UID field</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter ' OR 1=1 -- as UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Input should be treated as literal string, no injection</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2913,6 +5192,551 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>USERS_035</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Edge Case: User Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify user list with 10000+ users</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Open users tab on a platform with 10000+ users.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Users should load with pagination/infinite scroll. Alphabetical grouping should work.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>USERS_036</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify user with very long name</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a user with a 100+ character name in the list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Name should truncate with ellipsis. No layout breaking.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>USERS_037</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify user with special characters in name</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a user with emojis, unicode, or special chars in name.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Name should display correctly.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>USERS_038</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify user search with partial name</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Search for first 2 characters of a user's name.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>All users matching the partial name should appear.</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>USR_023</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Block/Unblock Rapid Toggle</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Rapid block/unblock</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid toggle handled correctly</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Block then immediately unblock
+2. Check status</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Final state correctly reflected</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>USR_024</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Section Headers - All Same Letter</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>All users start with 'A'</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify single section header</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Load users all starting with 'A'</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Single 'A' section header shown</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>USR_083</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Rapid Region Switching</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verify rapid switching between regions</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1. Click US, then EU, then IN rapidly
+2. Observe final state</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Only the last clicked region should be selected</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>USR_084</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Login - Rapid Multiple User Clicks</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Sample users displayed</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid clicking different sample users</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>1. Click user A
+2. Immediately click user B
+3. Observe behavior</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Only one login attempt should proceed, no race condition</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>USR_085</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>User Details - Rapid Block/Unblock</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>User details panel open</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Verify rapid block/unblock doesn't cause issues</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>1. Block user
+2. Immediately unblock
+3. Repeat rapidly</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Each action should complete before next, no race conditions</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>USERS_039</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify user list when server returns error</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Simulate server error.
+2. Open users tab.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Error message should display with retry option. No crash.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>USR_025</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Block Offline User</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Target user is offline</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Verify can block offline user</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1. Block an offline user</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>User blocked regardless of online status</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>USR_086</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Very Long App ID</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify handling of extremely long App ID</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter 1000+ character string as App ID
+2. Click Continue</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>App should handle gracefully, SDK init should fail with proper error</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2972,297 +5796,328 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>USERS_035</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Edge Case: User Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>USERS_040</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Boundary: User Module</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify user list with 10000+ users</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Open users tab on a platform with 10000+ users.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Users should load with pagination/infinite scroll. Alphabetical grouping should work.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify user list with exactly 0 users (only self)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Login on a platform with no other users.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Empty state should display or only self should appear.</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>USERS_036</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify user with very long name</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a user with a 100+ character name in the list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Name should truncate with ellipsis. No layout breaking.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>USERS_041</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify user list with exactly 1 other user</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Login on a platform with 1 other user.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Single user should display correctly with all elements.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>USERS_042</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify search with exactly 1 character</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Type a single character in user search.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Should filter users or show minimum character requirement.</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>USERS_037</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify user with special characters in name</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a user with emojis, unicode, or special chars in name.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Name should display correctly.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>USERS_038</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify user search with partial name</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Search for first 2 characters of a user's name.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>All users matching the partial name should appear.</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>USR_026</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Users List Limit 30</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Default limit</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify 30 users loaded initially</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Open users list</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>30 users loaded, more on scroll</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>USR_023</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Block/Unblock Rapid Toggle</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Rapid block/unblock</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify rapid toggle handled correctly</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Block then immediately unblock
-2. Check status</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Final state correctly reflected</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>USR_087</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Minimum Valid App ID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verify minimum length App ID (1 char)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter single character as App ID
+2. Enter valid Auth Key
+3. Submit</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Form should submit (HTML validation passes), SDK may reject</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>USR_024</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Section Headers - All Same Letter</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>All users start with 'A'</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify single section header</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. Load users all starting with 'A'</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Single 'A' section header shown</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>USR_088</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Login - Single Character UID</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Verify login with 1-character UID</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter single character UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Login attempt should be made with the single character UID</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+    </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>USERS_039</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>USR_027</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Verify user list when server returns error</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1. Simulate server error.
-2. Open users tab.</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Error message should display with retry option. No crash.</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Empty Users List</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>No users available</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state with 0 users</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1. No users in app</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Empty state displayed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>USR_025</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>USR_089</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Block Offline User</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Target user is offline</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Verify can block offline user</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1. Block an offline user</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>User blocked regardless of online status</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Login - Very Long UID</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify login with extremely long UID (500+ chars)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter 500+ character UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Should handle gracefully, SDK should reject or timeout</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -3271,14 +6126,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
+    <tabColor rgb="0000B0F0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3334,483 +6189,411 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>USERS_040</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Boundary: User Module</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>USERS_043</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: User Status</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify user list with exactly 0 users (only self)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Login on a platform with no other users.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Empty state should display or only self should appear.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Verify online user display</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe an online user in the list.</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Should show green online indicator and be at top of list (if sorted by status).</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>USERS_044</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Verify offline user display</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe an offline user in the list.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Should show grey/no indicator. Last seen time may display.</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>USERS_045</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Verify away/busy user display (if supported)</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>1. Observe a user with away/busy status.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Should show appropriate status indicator (yellow/red dot).</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>USERS_041</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify user list with exactly 1 other user</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Login on a platform with 1 other user.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Single user should display correctly with all elements.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>USERS_042</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify search with exactly 1 character</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Type a single character in user search.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Should filter users or show minimum character requirement.</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>USR_026</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Users List Limit 30</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Default limit</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify 30 users loaded initially</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Open users list</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>30 users loaded, more on scroll</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>USR_028</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Online User</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>User is online</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Verify online user display</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>1. Check online user in list</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Green status indicator, name, avatar shown</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>USR_029</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Offline User</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>User is offline</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify offline user display</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Check offline user in list</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Grey/no status indicator, name, avatar shown</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>USR_090</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Valid Hex App ID</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verify valid hexadecimal App ID format</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter valid hex string App ID
+2. Enter valid Auth Key
+3. Submit</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Credentials should be accepted and SDK initialized</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>USR_027</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>USR_091</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Login - Alphanumeric UID</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Verify login with alphanumeric UID</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>1. Enter UID like 'user123'
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Login should proceed normally</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>USR_030</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Empty Users List</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>No users available</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Verify empty state with 0 users</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>1. No users in app</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Empty state displayed</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0000B0F0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>TestCase_ID</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Test Scenario</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Precondition</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Test Case</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>Steps</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>Expected Results</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Priority/Severity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>USERS_043</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Equivalence Partitioning: User Status</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>Verify online user display</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe an online user in the list.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>Should show green online indicator and be at top of list (if sorted by status).</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>USERS_044</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Verify offline user display</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe an offline user in the list.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Should show grey/no indicator. Last seen time may display.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>USERS_045</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Verify away/busy user display (if supported)</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>1. Observe a user with away/busy status.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Should show appropriate status indicator (yellow/red dot).</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>USR_028</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Online User</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>User is online</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Verify online user display</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>1. Check online user in list</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Green status indicator, name, avatar shown</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>USR_029</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Offline User</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>User is offline</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>Verify offline user display</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1. Check offline user in list</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Grey/no status indicator, name, avatar shown</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>USR_030</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Blocked User</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>User is blocked</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verify blocked user display</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1. Check blocked user in list</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Blocked indicator or different styling shown</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>USR_092</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Blocked User</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>User is blocked</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>Verify blocked user display</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1. Check blocked user in list</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Blocked indicator or different styling shown</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Credentials - Special Chars in App ID</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Credentials screen displayed</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify special characters in App ID</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter App ID with special chars (!@#$%)
+2. Submit</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>SDK should reject invalid App ID format</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>USR_093</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Login - UID with Spaces</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Login screen displayed</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify login with UID containing spaces</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Enter 'user 123' as UID
+2. Click Login</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>SDK should handle or reject UID with spaces</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>

--- a/User_Module/Users_Module_Test_Script.xlsx
+++ b/User_Module/Users_Module_Test_Script.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,6 +107,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1705,7 +1711,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>USR_031</t>
+          <t>USR_048</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1715,1819 +1721,1030 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Credentials - Region Selection</t>
+          <t>User Details - Open Panel</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>App launched, credentials screen displayed</t>
+          <t>User conversation selected</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify US region is selected by default</t>
+          <t>Verify user details panel opens on header click</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1. Open app
-2. Navigate to credentials screen
-3. Observe region selector</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>US region should be pre-selected by default</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>USR_032</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Select EU Region</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Verify user can select EU region</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>1. Click on EU region option
-2. Observe selection state</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>EU region should be highlighted as selected, US deselected</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>USR_033</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Select IN Region</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>Verify user can select IN region</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>1. Click on IN region option
-2. Observe selection state</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>IN region should be highlighted as selected</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>USR_034</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Enter Valid App ID</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Verify user can enter App ID</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>1. Click App ID input field
-2. Type valid App ID
-3. Observe input</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>App ID should be accepted and displayed in the field</t>
-        </is>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>USR_035</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Enter Valid Auth Key</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Verify user can enter Auth Key</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>1. Click Auth Key input field
-2. Type valid Auth Key
-3. Observe input</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Auth Key should be accepted and displayed in the field</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>USR_036</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Submit Valid Credentials</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>All fields filled with valid data</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>Verify successful submission navigates to login</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>1. Enter valid App ID
-2. Enter valid Auth Key
-3. Select region
-4. Click Continue</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>CometChat SDK should initialize and navigate to /login page</t>
-        </is>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>USR_037</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - LocalStorage Persistence</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>Valid credentials entered</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>Verify credentials are saved to localStorage</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>1. Enter App ID, Auth Key, select region
-2. Click Continue
-3. Check localStorage</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>region, appId, authKey should be stored in localStorage</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>USR_038</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Credentials - Dark Mode Logo</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Dark mode enabled on device</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Verify dark mode logo is displayed</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>1. Enable dark mode in OS settings
-2. Open credentials screen
-3. Observe logo</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>Dark mode CometChat logo should be displayed</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>USR_039</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Light Mode Logo</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Light mode enabled on device</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Verify light mode logo is displayed</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable light mode in OS settings
-2. Open credentials screen
-3. Observe logo</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Light mode CometChat logo should be displayed</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>USR_040</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Login - Sample Users Display</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Login screen loaded, API accessible</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Verify sample users are fetched and displayed</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>1. Navigate to login screen
-2. Wait for users to load
-3. Observe user list</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Sample users should be fetched from API and displayed with avatar, name, and UID</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>USR_041</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Login - Sample User Click Login</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Sample users displayed</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify clicking a sample user logs in</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on a sample user card
-2. Wait for login
-3. Observe navigation</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>User should be logged in via CometChatUIKit.login() and navigated to /home</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>USR_042</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Login - Selection Indicator</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sample users displayed</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Verify selected user shows selection indicator</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Click on a sample user
-2. Observe visual feedback</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Selected user should show a checked selection indicator circle</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>USR_043</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Login - Custom UID Login</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Verify login with custom UID</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter a valid UID in the custom UID input
-2. Click Login button
-3. Wait for login</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>User should be logged in with the custom UID and navigated to /home</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>USR_044</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Login - Change App Credentials Link</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Verify Change App Credentials navigates to credentials screen</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1. Click 'App Credentials' link text
-2. Observe navigation</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Should clear localStorage credentials and navigate to /credentials</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>USR_045</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Login - Auto-redirect If Logged In</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>User already logged in</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Verify auto-redirect to home if already logged in</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Login successfully
-2. Navigate back to /login
-3. Observe behavior</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Should automatically redirect to /home with replace:true</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>USR_046</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Login - Fallback Sample Users</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>API endpoint unreachable</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Verify fallback sample users are used when API fails</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1. Block network to sample data API
-2. Navigate to login screen
-3. Observe user list</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Fallback sample users from local sampledata.ts should be displayed</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>USR_047</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Login - Dark Mode Logo</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Dark mode enabled</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Verify dark mode logo on login screen</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1. Enable dark mode
-2. Open login screen</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Dark mode CometChat logo should be displayed</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>USR_048</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>User Details - Open Panel</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>User conversation selected</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>Verify user details panel opens on header click</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Select a user conversation
 2. Click on message header
 3. Observe side panel</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>User details side panel should open showing avatar, name, status</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>USR_049</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>User Details - Block User Flow</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>User details panel open</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Verify block user with confirmation dialog</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>1. Click Block option
 2. Observe confirmation dialog
 3. Click Block in dialog</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog appears, user blocked on confirm, toast shows 'Blocked successfully'</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>USR_050</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>User Details - Unblock User</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>User is blocked, details panel open</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Verify unblock user action</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>1. Click Unblock option in details
 2. Observe behavior</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>User should be unblocked immediately (no confirmation), action text changes to Block</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>USR_051</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>User Details - Block Hides Status</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>User details panel open</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Verify blocking hides user status</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>1. Block a user
 2. Observe status indicator</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>User status (online/offline) should be hidden after blocking</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>USR_052</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>User Details - Unblock Shows Status</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Blocked user details panel open</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Verify unblocking restores status visibility</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>1. Unblock a user
 2. Observe status indicator</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>User status should become visible again after unblocking</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>USR_053</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>User Details - Delete Chat</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>User details panel open, conversation exists</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>Verify delete chat with confirmation</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>1. Click Delete Chat
 2. Observe confirmation dialog
 3. Confirm deletion</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>Confirmation dialog appears, conversation deleted, side panel closes, toast shown</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>USR_054</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>User Details - Close Panel</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>User details panel open</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Verify closing the details panel</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>1. Click close icon on panel
 2. Observe behavior</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>Side panel should close, messages view remains</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>USR_055</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>User Details - Block Confirmation Cancel</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Block confirmation dialog shown</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>Verify canceling block confirmation</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>1. Click Block
 2. In confirmation dialog click Cancel</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr">
         <is>
           <t>Dialog should close, user remains unblocked</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>USR_056</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>User Details - Delete Chat Confirmation Cancel</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Delete confirmation dialog shown</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Verify canceling delete confirmation</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1. Click Delete Chat
 2. In confirmation dialog click Cancel</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Dialog should close, conversation remains</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
+      <c r="H42" s="8" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>USERS_005</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Verify Users List display</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>User is logged in, no users exist</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Verify empty users list state</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab with no users in system.
 2. Observe display.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Appropriate empty state message should display (e.g., "No users found").</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>USERS_014</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Verify Search functionality</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>User is logged in and on Users tab</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Verify search with no matching results</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Navigate to Users tab.
 2. Type "XYZ123" in search field.
 3. Observe results.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Empty state should display with message like "No users found" or "No results".</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>USERS_024</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Verify Users List loading</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>User is logged in, slow network</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Verify loading state during slow connection</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Simulate slow network.
 2. Navigate to Users tab.
 3. Observe loading behavior.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Loading indicator should display while users list is being fetched.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>USR_010</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Block - Already Blocked</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>User already blocked</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Verify block option changes to unblock</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. Check blocked user options</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Only unblock option shown, not block</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>USR_011</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>View Profile - No Profile</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>User has minimal profile</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Verify handling of empty profile data</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. View profile of user with no details</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Appropriate fallback/empty state shown</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>USR_012</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>User Status Hidden</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>hideUserStatus=true</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Verify status indicator hidden</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Set hideUserStatus=true
 2. Check users</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>No online/offline indicators visible</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>USR_013</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Block Self</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Own profile</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Verify cannot block self</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Check own profile options</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Block option not available for self</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>USR_057</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>USR_064</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Empty App ID</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Verify form validation for empty App ID</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1. Leave App ID empty
-2. Enter Auth Key
-3. Click Continue</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Form should not submit, HTML5 required validation should trigger</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>USR_058</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Empty Auth Key</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Verify form validation for empty Auth Key</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter App ID
-2. Leave Auth Key empty
-3. Click Continue</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Form should not submit, HTML5 required validation should trigger</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>USR_059</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Invalid App ID</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Verify error handling for invalid App ID</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter invalid/random App ID
-2. Enter valid Auth Key
-3. Click Continue</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>SDK initialization should fail, appropriate error handling</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>USR_060</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Both Fields Empty</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Verify form won't submit with all fields empty</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Leave all fields empty
-2. Click Continue</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Form should not submit due to required field validation</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>USR_061</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Login - Empty Custom UID</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty UID validation</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>1. Leave UID field empty
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Form should not submit due to required field validation</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>USR_062</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Login - Invalid Custom UID</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Verify login with non-existent UID</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter non-existent UID
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Login should fail, error logged to console</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>USR_063</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Login - No Credentials Redirect</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>No credentials in localStorage or AppConstants</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Verify redirect to credentials when no credentials exist</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>1. Clear all localStorage
-2. Set empty AppConstants
-3. Navigate to /login</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Should redirect to /credentials screen</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>USR_064</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>User Details - Delete Fresh Chat</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fresh chat with no messages</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Verify delete chat disabled for fresh chats</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Start new chat (no messages sent)
 2. Open details
 3. Observe Delete Chat</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Delete Chat option should be visually disabled (action-item-disabled class)</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>USR_065</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>User Details - Delete Chat API Failure</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>User details panel open</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Verify error handling on delete chat failure</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Click Delete Chat
 2. Confirm
 3. Simulate API failure</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Error should be caught and logged, app should not crash</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n"/>
+      <c r="B52" s="8" t="n"/>
+      <c r="C52" s="8" t="n"/>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="8" t="n"/>
+      <c r="F52" s="8" t="n"/>
+      <c r="G52" s="8" t="n"/>
+      <c r="H52" s="8" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+      <c r="B53" s="8" t="n"/>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n"/>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
+      <c r="G54" s="8" t="n"/>
+      <c r="H54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="n"/>
+      <c r="B55" s="8" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="8" t="n"/>
+      <c r="F55" s="8" t="n"/>
+      <c r="G55" s="8" t="n"/>
+      <c r="H55" s="8" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n"/>
+      <c r="B56" s="8" t="n"/>
+      <c r="C56" s="8" t="n"/>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="8" t="n"/>
+      <c r="F56" s="8" t="n"/>
+      <c r="G56" s="8" t="n"/>
+      <c r="H56" s="8" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n"/>
+      <c r="B57" s="8" t="n"/>
+      <c r="C57" s="8" t="n"/>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="8" t="n"/>
+      <c r="F57" s="8" t="n"/>
+      <c r="G57" s="8" t="n"/>
+      <c r="H57" s="8" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n"/>
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+      <c r="G58" s="8" t="n"/>
+      <c r="H58" s="8" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+      <c r="H59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n"/>
+      <c r="B60" s="8" t="n"/>
+      <c r="C60" s="8" t="n"/>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="8" t="n"/>
+      <c r="F60" s="8" t="n"/>
+      <c r="G60" s="8" t="n"/>
+      <c r="H60" s="8" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n"/>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
+      <c r="G61" s="8" t="n"/>
+      <c r="H61" s="8" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n"/>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
+      <c r="G62" s="8" t="n"/>
+      <c r="H62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n"/>
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+      <c r="G63" s="8" t="n"/>
+      <c r="H63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n"/>
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+      <c r="G64" s="8" t="n"/>
+      <c r="H64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n"/>
+      <c r="B65" s="8" t="n"/>
+      <c r="C65" s="8" t="n"/>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="8" t="n"/>
+      <c r="F65" s="8" t="n"/>
+      <c r="G65" s="8" t="n"/>
+      <c r="H65" s="8" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n"/>
+      <c r="B66" s="8" t="n"/>
+      <c r="C66" s="8" t="n"/>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="8" t="n"/>
+      <c r="F66" s="8" t="n"/>
+      <c r="G66" s="8" t="n"/>
+      <c r="H66" s="8" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n"/>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+      <c r="G67" s="8" t="n"/>
+      <c r="H67" s="8" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
+      <c r="G68" s="8" t="n"/>
+      <c r="H68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n"/>
+      <c r="B69" s="8" t="n"/>
+      <c r="C69" s="8" t="n"/>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="8" t="n"/>
+      <c r="F69" s="8" t="n"/>
+      <c r="G69" s="8" t="n"/>
+      <c r="H69" s="8" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n"/>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
+      <c r="G70" s="8" t="n"/>
+      <c r="H70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n"/>
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+      <c r="G71" s="8" t="n"/>
+      <c r="H71" s="8" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n"/>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+      <c r="G72" s="8" t="n"/>
+      <c r="H72" s="8" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n"/>
+      <c r="B73" s="8" t="n"/>
+      <c r="C73" s="8" t="n"/>
+      <c r="D73" s="8" t="n"/>
+      <c r="E73" s="8" t="n"/>
+      <c r="F73" s="8" t="n"/>
+      <c r="G73" s="8" t="n"/>
+      <c r="H73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n"/>
+      <c r="B74" s="8" t="n"/>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n"/>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
+      <c r="G75" s="8" t="n"/>
+      <c r="H75" s="8" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n"/>
+      <c r="B76" s="7" t="n"/>
+      <c r="C76" s="7" t="n"/>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
+      <c r="F76" s="7" t="n"/>
+      <c r="G76" s="7" t="n"/>
+      <c r="H76" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3541,7 +2758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3805,7 +3022,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>USR_066</t>
+          <t>USR_070</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -3815,29 +3032,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Credentials - SDK Init Integration</t>
+          <t>User Details - Block Event Propagation</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Valid credentials available</t>
+          <t>User blocked from details</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Verify CometChat SDK initializes with provided credentials</t>
+          <t>Verify block event updates message composer</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1. Enter valid App ID, Auth Key, region
-2. Click Continue
-3. Monitor SDK init</t>
+          <t>1. Block user from details panel
+2. Observe message composer</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>UIKitSettingsBuilder should build with correct params, SDK init succeeds</t>
+          <t>Composer should be replaced with 'Cannot send to blocked user' message with unblock link</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -3849,7 +3065,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>USR_067</t>
+          <t>USR_071</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -3859,40 +3075,40 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Credentials - Navigation to Login</t>
+          <t>User Details - Unblock Event Propagation</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>SDK initialized successfully</t>
+          <t>User unblocked from details</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Verify navigation from credentials to login screen</t>
+          <t>Verify unblock event restores composer</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1. Submit valid credentials
-2. Observe navigation</t>
+          <t>1. Unblock user from details
+2. Observe message composer</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>App should navigate to /login route with replace:true</t>
+          <t>Message composer should reappear, blocked message removed</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>USR_068</t>
+          <t>USR_072</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3902,40 +3118,40 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Login - CometChatUIKit.login Integration</t>
+          <t>User Details - Delete Conversation Event</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Valid UID available</t>
+          <t>Chat deleted from details</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Verify CometChatUIKit.login() is called correctly</t>
+          <t>Verify conversation deleted event fires</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1. Click sample user or enter custom UID
-2. Monitor SDK login call</t>
+          <t>1. Delete chat from details
+2. Monitor events</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>CometChatUIKit.login(uid) should be called and return loggedInUser</t>
+          <t>ccConversationDeleted event should fire, conversation removed from list</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>USR_069</t>
+          <t>USR_073</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3945,294 +3161,148 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Login - Sample Users API Integration</t>
+          <t>User Details - Block Toast Notification</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Network available</t>
+          <t>User blocked</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Verify sample users fetched from correct API endpoint</t>
+          <t>Verify toast notification on block</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1. Open login screen
-2. Monitor network requests</t>
+          <t>1. Block a user
+2. Observe toast</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>GET request to https://assets.cc-cluster-2.io/sampleapp/v2/sampledata.json should be made</t>
+          <t>Toast should show 'Blocked successfully' message</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>USR_070</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>User Details - Block Event Propagation</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>User blocked from details</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify block event updates message composer</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1. Block user from details panel
-2. Observe message composer</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Composer should be replaced with 'Cannot send to blocked user' message with unblock link</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>USR_071</t>
+          <t>USR_017</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>User Details - Unblock Event Propagation</t>
+          <t>Block + Incoming Messages</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>User unblocked from details</t>
+          <t>User blocked</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Verify unblock event restores composer</t>
+          <t>Verify blocked user messages not received</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Unblock user from details
-2. Observe message composer</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Message composer should reappear, blocked message removed</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>USR_072</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>User Details - Delete Conversation Event</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Chat deleted from details</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation deleted event fires</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Delete chat from details
-2. Monitor events</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ccConversationDeleted event should fire, conversation removed from list</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>USR_073</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>User Details - Block Toast Notification</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>User blocked</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify toast notification on block</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Block a user
-2. Observe toast</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Toast should show 'Blocked successfully' message</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>USR_017</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Block + Incoming Messages</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User blocked</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify blocked user messages not received</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Block user
 2. Blocked user sends message</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Message not received or shown</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>USR_074</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - SDK Init Failure</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Invalid credentials entered</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Verify app handles SDK initialization failure</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter invalid credentials
-2. Click Continue
-3. Observe behavior</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>App should handle error gracefully without crashing</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4246,7 +3316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4527,7 +3597,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>USR_075</t>
+          <t>USR_077</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4537,109 +3607,20 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Credentials - Re-enter After Change</t>
+          <t>User Details - Block/Unblock Toggle</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Previously logged in, credentials changed</t>
+          <t>User details panel open</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify credentials screen works after clearing credentials</t>
+          <t>Verify Block/Unblock text toggles correctly</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Login successfully
-2. Change credentials from login screen
-3. Re-enter new credentials
-4. Submit</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>New credentials should be accepted and SDK re-initialized</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>USR_076</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Login - Re-login After Logout</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>User previously logged out</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Verify login works after logout</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. Logout from app
-2. Return to login screen
-3. Login again</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Login should work normally after logout</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>USR_077</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>User Details - Block/Unblock Toggle</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User details panel open</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify Block/Unblock text toggles correctly</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Block user
 2. Observe action text changes to Unblock
@@ -4647,59 +3628,99 @@
 4. Observe text changes to Block</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Action text should toggle between Block and Unblock correctly</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>USR_020</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Unblock After App Restart</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>User unblocked then app restarted</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify unblock persists after restart</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1. Unblock user
 2. Restart app</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>User still unblocked</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4713,7 +3734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4875,62 +3896,61 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>USR_078</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Auth Key Not Masked</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verify Auth Key input is plain text type</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter Auth Key
-2. Observe input type</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Auth Key field uses type='text' (visible for dev convenience)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
+      <c r="H5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n"/>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>USERS_032</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Security: User Module</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>User is not logged in</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Verify user list not accessible without authentication</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1. Try to access user list without logging in.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Should redirect to login. No user data exposed.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>USERS_032</t>
+          <t>USR_022</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -4940,248 +3960,94 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Security: User Module</t>
+          <t>Block Bypass via API</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>User is not logged in</t>
+          <t>Direct API call</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Verify user list not accessible without authentication</t>
+          <t>Verify block cannot be bypassed</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1. Try to access user list without logging in.</t>
+          <t>1. Try to message blocked user via API</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Should redirect to login. No user data exposed.</t>
+          <t>Message rejected for blocked user</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>High / Critical</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>USR_022</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Block Bypass via API</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Direct API call</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verify block cannot be bypassed</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to message blocked user via API</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Message rejected for blocked user</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
+      <c r="H8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>USR_079</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - XSS in App ID</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify XSS injection in App ID is handled</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as App ID
-2. Click Continue</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Script should not execute, input treated as plain text</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>USR_080</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - XSS in Auth Key</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify XSS injection in Auth Key is handled</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as Auth Key
-2. Click Continue</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Script should not execute, input treated as plain text</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>USR_081</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Login - XSS in Custom UID</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify XSS injection in UID field</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; as UID
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Script should not execute, treated as plain text UID</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>USR_082</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Login - SQL Injection in UID</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify SQL injection in UID field</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter ' OR 1=1 -- as UID
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Input should be treated as literal string, no injection</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5195,7 +4061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5470,7 +4336,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>USR_083</t>
+          <t>USR_085</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -5480,253 +4346,163 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Credentials - Rapid Region Switching</t>
+          <t>User Details - Rapid Block/Unblock</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Credentials screen displayed</t>
+          <t>User details panel open</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Verify rapid switching between regions</t>
+          <t>Verify rapid block/unblock doesn't cause issues</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1. Click US, then EU, then IN rapidly
-2. Observe final state</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Only the last clicked region should be selected</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>USR_084</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Login - Rapid Multiple User Clicks</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Sample users displayed</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Verify rapid clicking different sample users</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>1. Click user A
-2. Immediately click user B
-3. Observe behavior</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Only one login attempt should proceed, no race condition</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>USR_085</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>User Details - Rapid Block/Unblock</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>User details panel open</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Verify rapid block/unblock doesn't cause issues</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Block user
 2. Immediately unblock
 3. Repeat rapidly</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Each action should complete before next, no race conditions</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>USERS_039</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Verify user list when server returns error</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>1. Simulate server error.
 2. Open users tab.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Error message should display with retry option. No crash.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>USR_025</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Block Offline User</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Target user is offline</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Verify can block offline user</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1. Block an offline user</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>User blocked regardless of online status</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>USR_025</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Block Offline User</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Target user is offline</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Verify can block offline user</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1. Block an offline user</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>User blocked regardless of online status</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>USR_086</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Very Long App ID</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Verify handling of extremely long App ID</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter 1000+ character string as App ID
-2. Click Continue</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>App should handle gracefully, SDK init should fail with proper error</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5740,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5940,84 +4716,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>USR_087</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Minimum Valid App ID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verify minimum length App ID (1 char)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter single character as App ID
-2. Enter valid Auth Key
-3. Submit</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Form should submit (HTML validation passes), SDK may reject</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>USR_088</t>
+          <t>USR_027</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Login - Single Character UID</t>
+          <t>Empty Users List</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Login screen displayed</t>
+          <t>No users available</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Verify login with 1-character UID</t>
+          <t>Verify empty state with 0 users</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>1. Enter single character UID
-2. Click Login</t>
+          <t>1. No users in app</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Login attempt should be made with the single character UID</t>
+          <t>Empty state displayed</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -6037,89 +4778,34 @@
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>USR_027</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Empty Users List</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>No users available</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state with 0 users</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1. No users in app</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Empty state displayed</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>USR_089</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Login - Very Long UID</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify login with extremely long UID (500+ chars)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter 500+ character UID
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Should handle gracefully, SDK should reject or timeout</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6133,7 +4819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6375,84 +5061,49 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>USR_090</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Valid Hex App ID</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verify valid hexadecimal App ID format</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter valid hex string App ID
-2. Enter valid Auth Key
-3. Submit</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Credentials should be accepted and SDK initialized</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>USR_091</t>
+          <t>USR_030</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Login - Alphanumeric UID</t>
+          <t>Blocked User</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Login screen displayed</t>
+          <t>User is blocked</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Verify login with alphanumeric UID</t>
+          <t>Verify blocked user display</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>1. Enter UID like 'user123'
-2. Click Login</t>
+          <t>1. Check blocked user in list</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Login should proceed normally</t>
+          <t>Blocked indicator or different styling shown</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -6472,132 +5123,44 @@
       <c r="H9" s="7" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>USR_030</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Blocked User</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>User is blocked</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Verify blocked user display</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1. Check blocked user in list</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Blocked indicator or different styling shown</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>USR_092</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Credentials - Special Chars in App ID</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Credentials screen displayed</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Verify special characters in App ID</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter App ID with special chars (!@#$%)
-2. Submit</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>SDK should reject invalid App ID format</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>USR_093</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Login - UID with Spaces</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Login screen displayed</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify login with UID containing spaces</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter 'user 123' as UID
-2. Click Login</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>SDK should handle or reject UID with spaces</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
